--- a/data/raw/inventory/Week 29/Audio_Array/Vendor SOH (SP-API).xlsx
+++ b/data/raw/inventory/Week 29/Audio_Array/Vendor SOH (SP-API).xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,91 +413,91 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q141"/>
+  <dimension ref="A1:Q142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>ASIN</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>category_l0</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>category_l1</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>category_l2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>NLC</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Channel</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Week</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>OpenPOUnits</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Aged90PlusUnits</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>UnsellableUnits</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>SellableCost</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>SnapshotDate</t>
         </is>
@@ -518,12 +506,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FBK79009</t>
+          <t>FBA79982</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>B0FLYHJ6DK</t>
+          <t>B0GN8MPYPG</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -533,25 +521,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AM-C41</t>
+          <t>AK-61 Pro</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Electric Keyboard</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Tripod</t>
+          <t>61 Key Electronic Keyboard With LCD DIsplay</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>1043.232336</v>
+        <v>3317.4116676</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -563,32 +551,32 @@
         <v>29</v>
       </c>
       <c r="M2" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>26914.61</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FBA79824</t>
+          <t>FBA79846</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>B0FJ2K95XT</t>
+          <t>B0FN7C25VS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -598,22 +586,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>GB-01 (AM-C43 +AI-10)</t>
+          <t>AM-C11X Pro</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>GB-01</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>2585.9936</v>
+        <v>2263.0394</v>
       </c>
       <c r="I3" t="n">
         <v>11</v>
@@ -631,29 +619,29 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>46140.06</v>
+        <v>36141.32</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FBA80010</t>
+          <t>FBA79823</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>B0GW8ZQRFK</t>
+          <t>B0FJ2HZCVN</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -663,25 +651,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AM-C52</t>
+          <t>PB-01 (AM-C11 + AI-04)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vocal Microphone</t>
+          <t>PB-01</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>912.8282939999998</v>
+        <v>4859.948</v>
       </c>
       <c r="I4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -696,29 +684,29 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>12458.18</v>
+        <v>82498.16</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FBA76597</t>
+          <t>FBA79104</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>B0BQ7H7418</t>
+          <t>B0CM6NVLT9</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -728,25 +716,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AA-06</t>
+          <t>AI-11</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>598.3056269558823</v>
+        <v>847.6262729999999</v>
       </c>
       <c r="I5" t="n">
-        <v>70</v>
+        <v>151</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -761,29 +749,29 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="O5" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="P5" t="n">
-        <v>65363.46</v>
+        <v>163390.09</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FBA79355</t>
+          <t>FBA76864</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>B0D3M86SH1</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -793,25 +781,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AA-19BL</t>
+          <t>AI-04 Red</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>2973.2121576</v>
+        <v>2165.574481998618</v>
       </c>
       <c r="I6" t="n">
-        <v>27</v>
+        <v>870</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -823,32 +811,32 @@
         <v>29</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O6" t="n">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="P6" t="n">
-        <v>87904.99000000001</v>
+        <v>3077071.27</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FBA79105</t>
+          <t>FBA79908</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>B0CM6WH4ZT</t>
+          <t>B0FTVV1QJY</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -858,25 +846,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>AI-12</t>
+          <t>PB-14 (AM-C43+AH-40-SL+AI-12)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>PB-14</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>678.1010183999999</v>
+        <v>2280.5034</v>
       </c>
       <c r="I7" t="n">
-        <v>101</v>
+        <v>4</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -888,32 +876,32 @@
         <v>29</v>
       </c>
       <c r="M7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>95231.05</v>
+        <v>16218.84</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FBA79826</t>
+          <t>FBA79822</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B0FJ2LQT7K</t>
+          <t>B0FJ2J6MTF</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -923,7 +911,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PB-02 (AI-04 Red + AM-C11 + AA-05)</t>
+          <t>KB-01 (AM-W32 + AI-12)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -933,15 +921,15 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PB-02</t>
+          <t>KB-01</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>5118.2854</v>
+        <v>2630.5268</v>
       </c>
       <c r="I8" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -953,32 +941,32 @@
         <v>29</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>120811.9</v>
+        <v>99409.85000000001</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FBA79834</t>
+          <t>FBA78424</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>B0FJ8T4WXM</t>
+          <t>B0C55MY66L</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -988,25 +976,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>PB-05 (AA-05 + AM-C11 + AI-04)</t>
+          <t>AM-C37</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PB-05</t>
+          <t>USB/XLR Dynamic Mic</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>5118.2854</v>
+        <v>3103.426797881559</v>
       </c>
       <c r="I9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1021,29 +1009,29 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>73409.8</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FBA79449</t>
+          <t>FBA79380</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>B0DFMNGFTD</t>
+          <t>B0D3M1B4Z8</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1053,25 +1041,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>AM-W36</t>
+          <t>AM-C46</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Microphone Wireless Handheld</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Wireless Microphone</t>
+          <t>Condenser Mic with Boom Arm</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>4042.525302</v>
+        <v>2021.262651</v>
       </c>
       <c r="I10" t="n">
-        <v>21</v>
+        <v>298</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1086,29 +1074,29 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="P10" t="n">
-        <v>93308.60000000001</v>
+        <v>792266.62</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FBA79445</t>
+          <t>FBA79906</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>B0DFMLS8JG</t>
+          <t>B0FTVVLNS9</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1118,25 +1106,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AM-W32</t>
+          <t>PB-12 (AM-C11+AA-05+AI-04+AH-60-RD)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Microphone Wireless Handheld</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Wireless Microphone</t>
+          <t>PB-12</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>2167.31517804</v>
+        <v>6152.0362</v>
       </c>
       <c r="I11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1148,32 +1136,32 @@
         <v>29</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" t="n">
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>71574.49000000001</v>
+        <v>211423.58</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FBA79447</t>
+          <t>FBA79847</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>B0DFMLXD9S</t>
+          <t>B0FN7FYZM3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1183,25 +1171,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>AM-W34</t>
+          <t>PB-09 (AM-C45 + AI-06 + AA-05)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Microphone Wireless Handheld</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Wireless Microphone</t>
+          <t>PB-09</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>2360.3131602</v>
+        <v>4889.153</v>
       </c>
       <c r="I12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1213,7 +1201,7 @@
         <v>29</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>7</v>
@@ -1222,23 +1210,23 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>31526.62</v>
+        <v>39150.73</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FBA76730</t>
+          <t>FBA79981</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>B0BLKB6FRR</t>
+          <t>B0GN8MFDGZ</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1248,25 +1236,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>AM-C27</t>
+          <t>AK-61 Neo</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Electric Keyboard</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vocal Microphone</t>
+          <t>61 Key Electronic Keyboard With LED DIsplay</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>827.5708984229998</v>
+        <v>2870.1202068</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1281,29 +1269,29 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
         <v>2</v>
       </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
       <c r="P13" t="n">
-        <v>3021.51</v>
+        <v>45439.37</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FBA78203</t>
+          <t>FBA75692</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>B0C4YTNJG7</t>
+          <t>B0B4G1HPL5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1313,25 +1301,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>AM-C30</t>
+          <t>AM-C11</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>RGB USB Microphone Kit - Tripod</t>
+          <t>USB/XLR Dynamic Mic</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>3196.1775</v>
+        <v>2975.579697881559</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1346,29 +1334,29 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="O14" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="P14" t="n">
-        <v>4647.07</v>
+        <v>89131.53999999999</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FBA75691</t>
+          <t>FBA80003</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>B0B4G5JG4P</t>
+          <t>B0GW92TTMS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1378,7 +1366,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>AM-W14</t>
+          <t>AM-W32 Pro</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1388,15 +1376,15 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Wireless Microphone</t>
+          <t>Dual UHF Wireless Microphone With Receiver</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>3221.74692</v>
+        <v>3129.697008</v>
       </c>
       <c r="I15" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1408,32 +1396,32 @@
         <v>29</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>88716.13</v>
+        <v>61869.39</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FBA76862</t>
+          <t>FBA78976</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>B0BPLWW72Y</t>
+          <t>B0CF5SHL15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1443,25 +1431,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>AM-C28</t>
+          <t>AA-22</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Microphone Conference</t>
+          <t>Monitor Speakers Accessories</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Conference Microphone</t>
+          <t>Monitor Speaker Stand Pair</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>874.2436631991176</v>
+        <v>1722.835557825</v>
       </c>
       <c r="I16" t="n">
-        <v>188</v>
+        <v>26</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1473,32 +1461,32 @@
         <v>29</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="P16" t="n">
-        <v>223697.92</v>
+        <v>66026.89999999999</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FBA75683</t>
+          <t>FBA79965</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>B0B4G94VP3</t>
+          <t>B0G53PRM34</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1508,25 +1496,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>AA-03</t>
+          <t>AM-Mix6</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Audio Mixer</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>6 channels mixer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>179.9635942941177</v>
+        <v>4696.526757959999</v>
       </c>
       <c r="I17" t="n">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1538,7 +1526,7 @@
         <v>29</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -1547,23 +1535,23 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>18192.71</v>
+        <v>59775.97</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FBA79446</t>
+          <t>FBA80007</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>B0DFMMTWLY</t>
+          <t>B0GN2LHJY4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1573,25 +1561,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>AM-W33</t>
+          <t>MT-12</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Microphone Wireless Handheld</t>
+          <t>Audio Mixer</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Wireless Microphone</t>
+          <t>12 channels Mixer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>1194.50102472</v>
+        <v>4119.760313999999</v>
       </c>
       <c r="I18" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1603,32 +1591,32 @@
         <v>29</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P18" t="n">
-        <v>53069.79</v>
+        <v>74737.64999999999</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FBA79958</t>
+          <t>FBA79833</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>B0G3Q59X8C</t>
+          <t>B0FJ8PZ9H7</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1638,25 +1626,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>AM-W24</t>
+          <t>PB-04 (AI-04 Red + AM-C44 x 2)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>PB-04</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>905.00405148</v>
+        <v>7169.514799999999</v>
       </c>
       <c r="I19" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1671,29 +1659,29 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P19" t="n">
-        <v>64650.55</v>
+        <v>121653.73</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FBA75679</t>
+          <t>FBA75678</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>B0B4JRQP22</t>
+          <t>B0B4G8PH2P</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1703,7 +1691,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>AA-02</t>
+          <t>AA-01</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1718,10 +1706,10 @@
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>1330.281037275</v>
+        <v>1224.499030661912</v>
       </c>
       <c r="I20" t="n">
-        <v>152</v>
+        <v>33</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1733,32 +1721,32 @@
         <v>29</v>
       </c>
       <c r="M20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P20" t="n">
-        <v>257482.55</v>
+        <v>48433.97</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FBA78204</t>
+          <t>FBA79826</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>B0C4YT43Z3</t>
+          <t>B0FJ2LQT7K</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1768,25 +1756,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>AM-C31</t>
+          <t>PB-02 (AI-04 Red + AM-C11 + AA-05)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Tripod</t>
+          <t>PB-02</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>3835.413</v>
+        <v>5118.2854</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1801,27 +1789,29 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="P21" t="inlineStr"/>
+      <c r="P21" t="n">
+        <v>120811.9</v>
+      </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FBA77171</t>
+          <t>FBA79966</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>B0CH4VCD6R</t>
+          <t>B0G53KWRVW</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1831,25 +1821,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>AC-6XL</t>
+          <t>AM-Mix10</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Audio Mixer</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>10 channels mixer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>169.5252546</v>
+        <v>5808.86204274</v>
       </c>
       <c r="I22" t="n">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1861,32 +1851,32 @@
         <v>29</v>
       </c>
       <c r="M22" t="n">
+        <v>43</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
         <v>6</v>
       </c>
-      <c r="N22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" t="n">
-        <v>10</v>
-      </c>
       <c r="P22" t="n">
-        <v>76188.22</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FBA79010</t>
+          <t>FBA79230</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>B0CH4T2BJD</t>
+          <t>B0CX1XK5R6</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1896,25 +1886,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>AM-C42</t>
+          <t>AM-W46</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Speaker Karaoke</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Boomarm</t>
+          <t>Microphone with Speaker</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>1499.646483</v>
+        <v>4277.252577599999</v>
       </c>
       <c r="I23" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1929,29 +1919,29 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O23" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>43947.37</v>
+        <v>18315.74</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FBA78975</t>
+          <t>FBA79446</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>B0CF5TCQKL</t>
+          <t>B0DFMMTWLY</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1961,25 +1951,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>AA-21</t>
+          <t>AM-W33</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Monitor Speakers Accessories</t>
+          <t>Microphone Wireless Handheld</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Monitor Speaker Stand Pair</t>
+          <t>Wireless Microphone</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>1722.835557825</v>
+        <v>1194.50102472</v>
       </c>
       <c r="I24" t="n">
-        <v>188</v>
+        <v>36</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1991,32 +1981,32 @@
         <v>29</v>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O24" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="P24" t="n">
-        <v>466989.82</v>
+        <v>53069.79</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FBA78206</t>
+          <t>FBA79905</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>B0C4YSV3XL</t>
+          <t>B0FTVSH458</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2026,25 +2016,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>AM-W15</t>
+          <t>PB-11 (AM-C44+AA-05+AH-45-BK)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Wireless Mic with Charging Case</t>
+          <t>PB-11</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>11761.9332</v>
+        <v>3425.8468</v>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2059,29 +2049,29 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>16505.6</v>
+        <v>25797.25</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FBA80005</t>
+          <t>FBA75688</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>B0GW96CQMG</t>
+          <t>B0B4G763WS</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2091,7 +2081,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>T-835</t>
+          <t>AM-W12</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2101,15 +2091,15 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Quad UHF Wireless Microphone With Receiver Box</t>
+          <t>Wireless Microphone</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>6259.394015999999</v>
+        <v>1956.963080117647</v>
       </c>
       <c r="I26" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2121,32 +2111,32 @@
         <v>29</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>142206.19</v>
+        <v>32295.69</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FBA79016</t>
+          <t>FBA75687</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>B0CH4R1V6S</t>
+          <t>B0B4G5ZLTB</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2156,25 +2146,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>AM-C3a</t>
+          <t>AM-W11</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vocal Microphone</t>
+          <t>Wireless Microphone</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>521.6161679999999</v>
+        <v>2857.758705882353</v>
       </c>
       <c r="I27" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2186,32 +2176,32 @@
         <v>29</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P27" t="n">
-        <v>19005.74</v>
+        <v>1885.92</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FBA75690</t>
+          <t>FBA78925</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>B0B4K87PR4</t>
+          <t>B0CBC7QMNV</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2221,25 +2211,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>AM-C10</t>
+          <t>AM-C11X</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Microphone Conference</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Conference Microphone</t>
+          <t>XLR Dynamic Mic</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>2311.522194589411</v>
+        <v>2173.4007</v>
       </c>
       <c r="I28" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2251,32 +2241,32 @@
         <v>29</v>
       </c>
       <c r="M28" t="n">
+        <v>1</v>
+      </c>
+      <c r="N28" t="n">
         <v>3</v>
       </c>
-      <c r="N28" t="n">
-        <v>13</v>
-      </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>84199.19</v>
+        <v>51861.01</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FBA79964</t>
+          <t>FBA79009</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>B0G53KWRWH</t>
+          <t>B0CH4PMR8K</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2286,25 +2276,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>AM-Pro12</t>
+          <t>AM-C41</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Audio Mixer</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>12 channels Mixer</t>
+          <t>USB Microphone Kit - Tripod</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>13162.63420323</v>
+        <v>1043.232336</v>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2319,29 +2309,29 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P29" t="n">
-        <v>34958.98</v>
+        <v>53597.14</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>FBA79482</t>
+          <t>FBA79844</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>B0DXFPM4N2</t>
+          <t>B0FN7DYB2M</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2351,25 +2341,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>AM-S1</t>
+          <t>PB-08 (AM-C1 + AI-04)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Monitor Speakers</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Studio Monitor Speaker</t>
+          <t>PB-08</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>4486.010979600001</v>
+        <v>3358.8228</v>
       </c>
       <c r="I30" t="n">
-        <v>117</v>
+        <v>1</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -2381,32 +2371,32 @@
         <v>29</v>
       </c>
       <c r="M30" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="N30" t="n">
         <v>1</v>
       </c>
       <c r="O30" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="P30" t="n">
-        <v>761494.8199999999</v>
+        <v>5033.59</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>FBA78960</t>
+          <t>FBA79011</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>B0CBCB82MT</t>
+          <t>B0CH4RNWJX</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2416,7 +2406,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>AM-C39</t>
+          <t>AM-C43</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2426,15 +2416,15 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>XLR Microphone Kit - Tripod</t>
+          <t>XLR Microphone Kit - Boomarm</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>734.122339149</v>
+        <v>1304.04042</v>
       </c>
       <c r="I31" t="n">
-        <v>55</v>
+        <v>143</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2446,32 +2436,32 @@
         <v>29</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N31" t="n">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="O31" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="P31" t="n">
-        <v>68573.92</v>
+        <v>259528.14</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>FBA79064</t>
+          <t>FBA76728</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>B0CJR76Y7G</t>
+          <t>B0BLNCP74M</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2481,25 +2471,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>AA-25</t>
+          <t>AM-C25</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>USB Microphone Kit - Boomarm</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>326.010105</v>
+        <v>2157.615343358823</v>
       </c>
       <c r="I32" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2511,32 +2501,32 @@
         <v>29</v>
       </c>
       <c r="M32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>18819.55</v>
+        <v>1626.51</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FBA79380</t>
+          <t>FBA79838</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>B0D3M1B4Z8</t>
+          <t>B0FQBX8J17</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2546,25 +2536,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>AM-C46</t>
+          <t>AH-40 SL</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>DJ Headphone</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Condenser Mic with Boom Arm</t>
+          <t>DJ Headphone</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>2021.262651</v>
+        <v>477.9615959999999</v>
       </c>
       <c r="I33" t="n">
-        <v>304</v>
+        <v>184</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2579,29 +2569,29 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="P33" t="n">
-        <v>808274.29</v>
+        <v>169674.53</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>FBA80009</t>
+          <t>FBA79010</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>B0GW8R2RYM</t>
+          <t>B0CH4T2BJD</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2611,25 +2601,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>AM-C51</t>
+          <t>AM-C42</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vocal Microphone</t>
+          <t>USB Microphone Kit - Boomarm</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>912.8282939999998</v>
+        <v>1499.646483</v>
       </c>
       <c r="I34" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2644,29 +2634,29 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P34" t="n">
-        <v>18687.28</v>
+        <v>43947.37</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>FBA79957</t>
+          <t>FBA79816</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>B0G3Q517Y2</t>
+          <t>B0FPR962YS</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2676,7 +2666,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>AM-W23</t>
+          <t>AM-W22</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2691,10 +2681,10 @@
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>1566.15254442</v>
+        <v>1679.60406096</v>
       </c>
       <c r="I35" t="n">
-        <v>51</v>
+        <v>173</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2709,29 +2699,29 @@
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>51</v>
+        <v>164</v>
       </c>
       <c r="O35" t="n">
         <v>1</v>
       </c>
       <c r="P35" t="n">
-        <v>120235.88</v>
+        <v>435345.64</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>FBA79844</t>
+          <t>FBA79109</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>B0FN7DYB2M</t>
+          <t>B0CM9HYVDM</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2741,25 +2731,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>PB-08 (AM-C1 + AI-04)</t>
+          <t>AM-W18</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Speaker Karaoke</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>PB-08</t>
+          <t>Microphone with Speaker</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>3358.8228</v>
+        <v>612.8989974</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>235</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2771,32 +2761,32 @@
         <v>29</v>
       </c>
       <c r="M36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="O36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P36" t="n">
-        <v>5033.59</v>
+        <v>205107.74</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>FBA79722</t>
+          <t>FBA80010</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>B0F2HYY7JF</t>
+          <t>B0GW8ZQRFK</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2806,25 +2796,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>AM-W21</t>
+          <t>AM-C52</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>Vocal Microphone</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>2803.686903</v>
+        <v>912.8282939999998</v>
       </c>
       <c r="I37" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2845,23 +2835,23 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>14763.09</v>
+        <v>12458.18</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>FBA79005</t>
+          <t>FBK79010</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>B0CKHVHVQ1</t>
+          <t>B0FLYJFC22</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2871,25 +2861,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>AM-W45</t>
+          <t>AM-C42</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Microphone Conference</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Wireless Conference Microphone</t>
+          <t>USB Microphone Kit - Boomarm</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>2738.484882</v>
+        <v>1499.646483</v>
       </c>
       <c r="I38" t="n">
-        <v>562</v>
+        <v>12</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2901,32 +2891,32 @@
         <v>29</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="P38" t="n">
-        <v>2151244.9</v>
+        <v>21418.21</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>FBA75689</t>
+          <t>FBA79957</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>B0B4G59Y8W</t>
+          <t>B0G3Q517Y2</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2936,25 +2926,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>AM-W13</t>
+          <t>AM-W23</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Microphone Wireless Handheld</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Wireless Microphone</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
-        <v>1305.459898830882</v>
+        <v>1566.15254442</v>
       </c>
       <c r="I39" t="n">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2969,29 +2959,29 @@
         <v>0</v>
       </c>
       <c r="N39" t="n">
+        <v>51</v>
+      </c>
+      <c r="O39" t="n">
         <v>1</v>
       </c>
-      <c r="O39" t="n">
-        <v>4</v>
-      </c>
       <c r="P39" t="n">
-        <v>34308.4</v>
+        <v>120235.88</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>FBA75692</t>
+          <t>FBA79103</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>B0B4G1HPL5</t>
+          <t>B0CM6NTWBP</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3001,25 +2991,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>AM-C11</t>
+          <t>AI-10</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>USB/XLR Dynamic Mic</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
-        <v>2975.579697881559</v>
+        <v>1499.646483</v>
       </c>
       <c r="I40" t="n">
-        <v>25</v>
+        <v>179</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -3034,29 +3024,29 @@
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>10</v>
+        <v>128</v>
       </c>
       <c r="O40" t="n">
         <v>12</v>
       </c>
       <c r="P40" t="n">
-        <v>89131.53999999999</v>
+        <v>386100.53</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FBA79845</t>
+          <t>FBA79708</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>B0FN7B3KWS</t>
+          <t>B0FFB6YJM1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3066,25 +3056,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>UB-02 (AM-S1 + AA-21)</t>
+          <t>SB-01</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Sound Bar</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UB-02</t>
+          <t>Sound Bar</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
-        <v>5836.846399999999</v>
+        <v>708</v>
       </c>
       <c r="I41" t="n">
-        <v>27</v>
+        <v>172</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -3096,32 +3086,32 @@
         <v>29</v>
       </c>
       <c r="M41" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="P41" t="n">
-        <v>263232.76</v>
+        <v>164979.95</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>FBA75688</t>
+          <t>FBA79835</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>B0B4G763WS</t>
+          <t>B0FJ8TWCQZ</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3131,25 +3121,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>AM-W12</t>
+          <t>PB-06 (AA-05 + AM-C44 + AI-04)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Microphone Wireless Handheld</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Wireless Microphone</t>
+          <t>PB-06</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
-        <v>1956.963080117647</v>
+        <v>4841.8232</v>
       </c>
       <c r="I42" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -3161,32 +3151,32 @@
         <v>29</v>
       </c>
       <c r="M42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>32295.69</v>
+        <v>118574.49</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FBA79465</t>
+          <t>FBA78974</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>B0DFMQCGT1</t>
+          <t>B0CF5RRTDJ</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3196,25 +3186,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>AM-W21</t>
+          <t>AA-20</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>2803.686903</v>
+        <v>1107.780080664706</v>
       </c>
       <c r="I43" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -3226,32 +3216,32 @@
         <v>29</v>
       </c>
       <c r="M43" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P43" t="n">
-        <v>34447.2</v>
+        <v>24455.75</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FBA79830</t>
+          <t>FBA78973</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>B0FJ8TSQK1</t>
+          <t>B0CF5R3V95</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3261,25 +3251,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>GB-03 (AI-12 + AM-C43)</t>
+          <t>AA-19</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>GB-03</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>1828.2802</v>
+        <v>1960.237563966397</v>
       </c>
       <c r="I44" t="n">
-        <v>20</v>
+        <v>121</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -3294,29 +3284,29 @@
         <v>1</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O44" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P44" t="n">
-        <v>58719.44</v>
+        <v>317484.46</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>FBA79820</t>
+          <t>FBA78975</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>B0FQJWWDVK</t>
+          <t>B0CF5TCQKL</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3326,25 +3316,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>AC-3XL</t>
+          <t>AA-21</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Monitor Speakers Accessories</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Monitor Speaker Stand Pair</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>130.404042</v>
+        <v>1722.835557825</v>
       </c>
       <c r="I45" t="n">
-        <v>49</v>
+        <v>187</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -3356,32 +3346,32 @@
         <v>29</v>
       </c>
       <c r="M45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N45" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="O45" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="P45" t="n">
-        <v>17099.41</v>
+        <v>464511.44</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FBA79980</t>
+          <t>FBK79009</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>B0GN8MMKY1</t>
+          <t>B0FLYHJ6DK</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3391,25 +3381,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>AK-37-W</t>
+          <t>AM-C41</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Electric Keyboard</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>37 Key Electronic Keyboard White</t>
+          <t>USB Microphone Kit - Tripod</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
-        <v>2335.8554064</v>
+        <v>1043.232336</v>
       </c>
       <c r="I46" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -3421,32 +3411,32 @@
         <v>29</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
         <v>1</v>
       </c>
-      <c r="O46" t="n">
-        <v>3</v>
-      </c>
       <c r="P46" t="n">
-        <v>13980.65</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FBA78925</t>
+          <t>FBA79964</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>B0CBC7QMNV</t>
+          <t>B0G53KWRWH</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3456,25 +3446,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>AM-C11X</t>
+          <t>AM-Pro12</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Audio Mixer</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>XLR Dynamic Mic</t>
+          <t>12 channels Mixer</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
-        <v>2173.4007</v>
+        <v>13162.63420323</v>
       </c>
       <c r="I47" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -3486,32 +3476,32 @@
         <v>29</v>
       </c>
       <c r="M47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>49134.79</v>
+        <v>34958.98</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FBA79230</t>
+          <t>FBA76863</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>B0CX1XK5R6</t>
+          <t>B0BPM2T7BQ</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3521,25 +3511,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>AM-W46</t>
+          <t>AI-03</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Speaker Karaoke</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Microphone with Speaker</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>4277.252577599999</v>
+        <v>2179.9269789525</v>
       </c>
       <c r="I48" t="n">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -3551,32 +3541,32 @@
         <v>29</v>
       </c>
       <c r="M48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P48" t="n">
-        <v>18315.74</v>
+        <v>152083.17</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>FBA79655</t>
+          <t>FBA79969</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>B0DN6PFWNK</t>
+          <t>B0G3B677Z5</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3586,25 +3576,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>AM-C44 Pro</t>
+          <t>UB-03 (AM-S1 + AA-22)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>UB-03</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
-        <v>3277.450944</v>
+        <v>5619.632</v>
       </c>
       <c r="I49" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -3616,32 +3606,32 @@
         <v>29</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N49" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>100388.06</v>
+        <v>163601.96</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>FBA79981</t>
+          <t>FBA78203</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>B0GN8MFDGZ</t>
+          <t>B0C4YTNJG7</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3651,25 +3641,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>AK-61 Neo</t>
+          <t>AM-C30</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Electric Keyboard</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61 Key Electronic Keyboard With LED DIsplay</t>
+          <t>RGB USB Microphone Kit - Tripod</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>2870.1202068</v>
+        <v>3196.1775</v>
       </c>
       <c r="I50" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -3684,29 +3674,29 @@
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P50" t="n">
-        <v>48934.71</v>
+        <v>3165.42</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FBA79979</t>
+          <t>FBA79465</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>B0GN8RQJRG</t>
+          <t>B0DFMQCGT1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3716,25 +3706,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>AK-37-B</t>
+          <t>AM-W21</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Electric Keyboard</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>37 Key Electronic Keyboard Black</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
-        <v>2261.3068296</v>
+        <v>2803.686903</v>
       </c>
       <c r="I51" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -3746,32 +3736,32 @@
         <v>29</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N51" t="n">
         <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>64311.01</v>
+        <v>34447.2</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>FBA76727</t>
+          <t>FBA79830</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>B0BLKCDRNB</t>
+          <t>B0FJ8TSQK1</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3781,25 +3771,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>AM-C24</t>
+          <t>GB-03 (AI-12 + AM-C43)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Tripod</t>
+          <t>GB-03</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
-        <v>1676.644024574118</v>
+        <v>1828.2802</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -3817,26 +3807,26 @@
         <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>61655.41</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FBA79960</t>
+          <t>FBA80004</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>B0G3B152FR</t>
+          <t>B0GW92316G</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3846,25 +3836,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>AM-W47 Wireless</t>
+          <t>AM-W36 Pro</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Voice Amplifier</t>
+          <t>Microphone Wireless Handheld</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Wireless Voice Amplifier</t>
+          <t>Dual UHF Wireless Microphone With Receiver Box</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
-        <v>920.65253652</v>
+        <v>4694.545512</v>
       </c>
       <c r="I53" t="n">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -3876,32 +3866,32 @@
         <v>29</v>
       </c>
       <c r="M53" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>85599.87</v>
+        <v>106966.25</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FBA79968</t>
+          <t>FBA79959</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>B0G53M9258</t>
+          <t>B0G39ZHDYP</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3911,25 +3901,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>AI-14</t>
+          <t>AM-W47 Wired</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Audio Mixer</t>
+          <t>Voice Amplifier</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>8 channels Mixer</t>
+          <t>Wired Voice Amplifier</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
-        <v>3065.101673616</v>
+        <v>503.35960212</v>
       </c>
       <c r="I54" t="n">
-        <v>91</v>
+        <v>120</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -3944,29 +3934,29 @@
         <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O54" t="n">
         <v>4</v>
       </c>
       <c r="P54" t="n">
-        <v>455260.56</v>
+        <v>115102.29</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FBA79813</t>
+          <t>FBA79827</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>B0FG88HVQ8</t>
+          <t>B0FJ8S5XJ8</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3976,25 +3966,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>AH-50</t>
+          <t>PB-03 (AI-04 Red + AM-C11 x 2)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>DJ Headphone</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>DJ Headphone</t>
+          <t>PB-03</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
-        <v>1201.7320128</v>
+        <v>7722.439199999999</v>
       </c>
       <c r="I55" t="n">
-        <v>544</v>
+        <v>15</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -4009,29 +3999,29 @@
         <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="O55" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>806015.99</v>
+        <v>155003.82</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>FBA79822</t>
+          <t>FBA79907</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>B0FJ2J6MTF</t>
+          <t>B0FTVS34SD</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4041,7 +4031,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>KB-01 (AM-W32 + AI-12)</t>
+          <t>PB-13 (AM-C43+AH-40-SL+AI-11)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -4051,15 +4041,15 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>KB-01</t>
+          <t>PB-13</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
-        <v>2630.5268</v>
+        <v>2436.8652</v>
       </c>
       <c r="I56" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -4071,32 +4061,30 @@
         <v>29</v>
       </c>
       <c r="M56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="P56" t="n">
-        <v>99409.85000000001</v>
-      </c>
+      <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FBA75674</t>
+          <t>FBA75689</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>B0B4G19R58</t>
+          <t>B0B4G59Y8W</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4106,25 +4094,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>AM-C2</t>
+          <t>AM-W13</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Microphone Wireless Handheld</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>XLR Microphone Kit - Boomarm</t>
+          <t>Wireless Microphone</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
-        <v>2119.874127397059</v>
+        <v>1305.459898830882</v>
       </c>
       <c r="I57" t="n">
-        <v>95</v>
+        <v>20</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -4136,32 +4124,32 @@
         <v>29</v>
       </c>
       <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
         <v>1</v>
       </c>
-      <c r="N57" t="n">
-        <v>8</v>
-      </c>
       <c r="O57" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="P57" t="n">
-        <v>275981.36</v>
+        <v>32691.99</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FBA76725</t>
+          <t>FBA79848</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>B0BLKCSJ7Z</t>
+          <t>B0GN97RFPR</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4171,25 +4159,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>AM-C22</t>
+          <t>AM-S2</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Monitor Speakers</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Tripod</t>
+          <t>Studio Monitor Speaker</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>849.3751611646587</v>
+        <v>3748.5845172</v>
       </c>
       <c r="I58" t="n">
-        <v>3</v>
+        <v>362</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -4204,29 +4192,29 @@
         <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>1865928.8</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FBA79827</t>
+          <t>FBA79106</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>B0FJ8S5XJ8</t>
+          <t>B0CM9KJZWQ</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4236,25 +4224,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>PB-03 (AI-04 Red + AM-C11 x 2)</t>
+          <t>AM-C44</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>PB-03</t>
+          <t>Dynamic Microphone</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
-        <v>7722.439199999999</v>
+        <v>2738.484882</v>
       </c>
       <c r="I59" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -4269,29 +4257,29 @@
         <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P59" t="n">
-        <v>155003.82</v>
+        <v>119737.23</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FBA78424</t>
+          <t>FBA78961</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>B0C55MY66L</t>
+          <t>B0CBCB9S14</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4301,25 +4289,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>AM-C37</t>
+          <t>AM-C40</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>USB/XLR Dynamic Mic</t>
+          <t>Condenser Mic with Boom Arm</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
-        <v>3103.426797881559</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -4334,29 +4322,29 @@
         <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O60" t="n">
         <v>1</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>4243.48</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FBA75686</t>
+          <t>FBA79694</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>B0B4G89VQJ</t>
+          <t>B0DT6T6N6B</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4366,25 +4354,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>AM-W10</t>
+          <t>AA-26</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Wireless Microphone</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
-        <v>4934.296426588235</v>
+        <v>260.808084</v>
       </c>
       <c r="I61" t="n">
-        <v>6</v>
+        <v>381</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -4396,32 +4384,32 @@
         <v>29</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N61" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="P61" t="n">
-        <v>21111.87</v>
+        <v>157302.05</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FBA79444</t>
+          <t>FBA79996</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>B0DFMLQBMC</t>
+          <t>B0GW8Z556N</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4431,25 +4419,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>AM-W20</t>
+          <t>AM-C49</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>Vocal Microphone</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
-        <v>2164.7070972</v>
+        <v>534.6565721999999</v>
       </c>
       <c r="I62" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -4461,32 +4449,32 @@
         <v>29</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N62" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>12578.82</v>
+        <v>8312.059999999999</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FBA79906</t>
+          <t>FBA79108</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>B0FTVVLNS9</t>
+          <t>B0CM9L1QZG</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4496,25 +4484,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>PB-12 (AM-C11+AA-05+AI-04+AH-60-RD)</t>
+          <t>AM-W16</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>PB-12</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
-        <v>6152.0362</v>
+        <v>756.3434436</v>
       </c>
       <c r="I63" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -4526,32 +4514,32 @@
         <v>29</v>
       </c>
       <c r="M63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P63" t="n">
-        <v>211423.58</v>
+        <v>45965.17</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>FBA79783</t>
+          <t>FBA75686</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>B0FF9R3GKK</t>
+          <t>B0B4G89VQJ</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4561,25 +4549,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>AM-C47</t>
+          <t>AM-W10</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Boomarm</t>
+          <t>Wireless Microphone</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
-        <v>1693.3496544</v>
+        <v>4934.296426588235</v>
       </c>
       <c r="I64" t="n">
-        <v>70</v>
+        <v>6</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -4594,29 +4582,29 @@
         <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O64" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P64" t="n">
-        <v>155798.52</v>
+        <v>21111.87</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FBA79982</t>
+          <t>FBA75676</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>B0GN8MPYPG</t>
+          <t>B0B4DS678Q</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4626,25 +4614,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>AK-61 Pro</t>
+          <t>AM-C4</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Electric Keyboard</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61 Key Electronic Keyboard With LCD DIsplay</t>
+          <t>USB Microphone Kit - Tripod</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
-        <v>3317.4116676</v>
+        <v>1700.734990628047</v>
       </c>
       <c r="I65" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -4656,32 +4644,32 @@
         <v>29</v>
       </c>
       <c r="M65" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O65" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="P65" t="n">
-        <v>26914.61</v>
+        <v>14089.43</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>FBA75678</t>
+          <t>FBA79836</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>B0B4G8PH2P</t>
+          <t>B0FJ8Z1W81</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4691,25 +4679,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>AA-01</t>
+          <t>PB-07 (AA-05 + AM-C45 + AI-04)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>PB-07</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
-        <v>1224.499030661912</v>
+        <v>4180.2798</v>
       </c>
       <c r="I66" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -4724,29 +4712,29 @@
         <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O66" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>51369.36</v>
+        <v>81238.77</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>FBA79966</t>
+          <t>FBA79958</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>B0G53KWRVW</t>
+          <t>B0G3Q59X8C</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4756,25 +4744,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>AM-Mix10</t>
+          <t>AM-W24</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Audio Mixer</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>10 channels mixer</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
-        <v>5808.86204274</v>
+        <v>905.00405148</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -4786,32 +4774,32 @@
         <v>29</v>
       </c>
       <c r="M67" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="O67" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>64650.55</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>FBA79109</t>
+          <t>FBA79821</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>B0CM9HYVDM</t>
+          <t>B0FJ2JJZL3</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4821,25 +4809,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>AM-W18</t>
+          <t>UB-01 (AI-04, AM-S1, AA-21, AM-C2)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Speaker Karaoke</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Microphone with Speaker</t>
+          <t>UB-01</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
-        <v>612.8989974</v>
+        <v>9527.5088</v>
       </c>
       <c r="I68" t="n">
-        <v>237</v>
+        <v>22</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -4851,32 +4839,32 @@
         <v>29</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N68" t="n">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="O68" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P68" t="n">
-        <v>206853.34</v>
+        <v>357978.96</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>FBA75681</t>
+          <t>FBA79016</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>B0B4FZS38V</t>
+          <t>B0CH4R1V6S</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4886,25 +4874,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>AM-C7</t>
+          <t>AM-C3a</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Boomarm</t>
+          <t>Vocal Microphone</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>2051.276637829411</v>
+        <v>521.6161679999999</v>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -4919,29 +4907,29 @@
         <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P69" t="n">
-        <v>2050.99</v>
+        <v>19005.74</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>FBK79010</t>
+          <t>FBA79722</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>B0FLYJFC22</t>
+          <t>B0F2HYY7JF</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4951,25 +4939,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>AM-C42</t>
+          <t>AM-W21</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Boomarm</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
-        <v>1499.646483</v>
+        <v>2803.686903</v>
       </c>
       <c r="I70" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -4981,32 +4969,32 @@
         <v>29</v>
       </c>
       <c r="M70" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
         <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>21418.21</v>
+        <v>14763.09</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>FBA79905</t>
+          <t>FBA79064</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>B0FTVSH458</t>
+          <t>B0CJR76Y7G</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5016,25 +5004,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>PB-11 (AM-C44+AA-05+AH-45-BK)</t>
+          <t>AA-25</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>PB-11</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
-        <v>3425.8468</v>
+        <v>326.010105</v>
       </c>
       <c r="I71" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -5046,32 +5034,32 @@
         <v>29</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N71" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P71" t="n">
-        <v>25797.25</v>
+        <v>18819.55</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>FBA79965</t>
+          <t>FBA79783</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>B0G53PRM34</t>
+          <t>B0FF9R3GKK</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5081,25 +5069,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>AM-Mix6</t>
+          <t>AM-C47</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Audio Mixer</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>6 channels mixer</t>
+          <t>USB Microphone Kit - Boomarm</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
-        <v>4696.526757959999</v>
+        <v>1693.3496544</v>
       </c>
       <c r="I72" t="n">
-        <v>9</v>
+        <v>68</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -5111,32 +5099,32 @@
         <v>29</v>
       </c>
       <c r="M72" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P72" t="n">
-        <v>59775.97</v>
+        <v>151352.91</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>FBA76864</t>
+          <t>FBA79379</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0D3LZWTHV</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5146,25 +5134,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>AI-04 Red</t>
+          <t>AM-C45</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>Dynamic Microphone</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
-        <v>2165.574481998618</v>
+        <v>2021.262651</v>
       </c>
       <c r="I73" t="n">
-        <v>884</v>
+        <v>29</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -5176,32 +5164,32 @@
         <v>29</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N73" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="O73" t="n">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="P73" t="n">
-        <v>3125586.44</v>
+        <v>74497.81</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>FBA79835</t>
+          <t>FBA79825</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>B0FJ8TWCQZ</t>
+          <t>B0FJ2DT13L</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5211,7 +5199,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>PB-06 (AA-05 + AM-C44 + AI-04)</t>
+          <t>GB-02 (AM-C43 + AI-11)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -5221,15 +5209,15 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>PB-06</t>
+          <t>GB-02</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
-        <v>4841.8232</v>
+        <v>1983.58</v>
       </c>
       <c r="I74" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -5244,29 +5232,29 @@
         <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>118574.49</v>
+        <v>63123.84</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>FBA79846</t>
+          <t>FBA78960</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>B0FN7C25VS</t>
+          <t>B0CBCB82MT</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5276,25 +5264,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>AM-C11X Pro</t>
+          <t>AM-C39</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>XLR Microphone Kit - Tripod</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
-        <v>2263.0394</v>
+        <v>734.122339149</v>
       </c>
       <c r="I75" t="n">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -5309,29 +5297,29 @@
         <v>0</v>
       </c>
       <c r="N75" t="n">
+        <v>18</v>
+      </c>
+      <c r="O75" t="n">
         <v>11</v>
       </c>
-      <c r="O75" t="n">
-        <v>0</v>
-      </c>
       <c r="P75" t="n">
-        <v>36141.32</v>
+        <v>68573.92</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>FBA79011</t>
+          <t>FBA75677</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>B0CH4RNWJX</t>
+          <t>B0B4KC7VBM</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5341,25 +5329,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>AM-C43</t>
+          <t>AM-C5</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Microphone Conference</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>XLR Microphone Kit - Boomarm</t>
+          <t>Conference Microphone</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
-        <v>1304.04042</v>
+        <v>1291.959696295941</v>
       </c>
       <c r="I76" t="n">
-        <v>145</v>
+        <v>80</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -5371,32 +5359,32 @@
         <v>29</v>
       </c>
       <c r="M76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>72</v>
+        <v>6</v>
       </c>
       <c r="O76" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="P76" t="n">
-        <v>263165.21</v>
+        <v>136640.87</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>FBA80007</t>
+          <t>FBA80005</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>B0GN2LHJY4</t>
+          <t>B0GW96CQMG</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5406,25 +5394,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>MT-12</t>
+          <t>T-835</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Audio Mixer</t>
+          <t>Microphone Wireless Handheld</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>12 channels Mixer</t>
+          <t>Quad UHF Wireless Microphone With Receiver Box</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
-        <v>4119.760313999999</v>
+        <v>6259.394015999999</v>
       </c>
       <c r="I77" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -5436,32 +5424,32 @@
         <v>29</v>
       </c>
       <c r="M77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>74527.89</v>
+        <v>142206.19</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>FBA79908</t>
+          <t>FBA79839</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>B0FTVV1QJY</t>
+          <t>B0FQBXS6Y2</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5471,25 +5459,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>PB-14 (AM-C43+AH-40-SL+AI-12)</t>
+          <t>AH-45 BK</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>DJ Headphone</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>PB-14</t>
+          <t>DJ Headphone</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
-        <v>2280.5034</v>
+        <v>614.5220519999999</v>
       </c>
       <c r="I78" t="n">
-        <v>3</v>
+        <v>217</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -5501,32 +5489,32 @@
         <v>29</v>
       </c>
       <c r="M78" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="N78" t="n">
         <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="P78" t="n">
-        <v>12164.13</v>
+        <v>240999.64</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>FBA79694</t>
+          <t>FBA79842</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>B0DT6T6N6B</t>
+          <t>B0G4DNF8RZ</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5536,25 +5524,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>AA-26</t>
+          <t>AM-C48</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
-        <v>260.808084</v>
+        <v>1956.06063</v>
       </c>
       <c r="I79" t="n">
-        <v>372</v>
+        <v>55</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -5566,32 +5554,32 @@
         <v>29</v>
       </c>
       <c r="M79" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
         <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="P79" t="n">
-        <v>153652.82</v>
+        <v>142250.59</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>FBA79961</t>
+          <t>FBA75690</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>B0G53H49BS</t>
+          <t>B0B4K87PR4</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5601,25 +5589,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>AI-13</t>
+          <t>AM-C10</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Audio Mixer</t>
+          <t>Microphone Conference</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>4 channels Mixer</t>
+          <t>Conference Microphone</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
-        <v>1544.91011775</v>
+        <v>2311.522194589411</v>
       </c>
       <c r="I80" t="n">
-        <v>479</v>
+        <v>28</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -5631,32 +5619,32 @@
         <v>29</v>
       </c>
       <c r="M80" t="n">
-        <v>93</v>
+        <v>3</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O80" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>1014797.45</v>
+        <v>81298.17999999999</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>FBA79836</t>
+          <t>FBA75681</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>B0FJ8Z1W81</t>
+          <t>B0B4FZS38V</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5666,25 +5654,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>PB-07 (AA-05 + AM-C45 + AI-04)</t>
+          <t>AM-C7</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>PB-07</t>
+          <t>USB Microphone Kit - Boomarm</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
-        <v>4180.2798</v>
+        <v>2051.276637829411</v>
       </c>
       <c r="I81" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -5699,29 +5687,29 @@
         <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>81238.77</v>
+        <v>2050.99</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>FBA79996</t>
+          <t>FBA79482</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>B0GW8Z556N</t>
+          <t>B0DXFPM4N2</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5731,25 +5719,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>AM-C49</t>
+          <t>AM-S1</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Monitor Speakers</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vocal Microphone</t>
+          <t>Studio Monitor Speaker</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
-        <v>534.6565721999999</v>
+        <v>4486.010979600001</v>
       </c>
       <c r="I82" t="n">
-        <v>9</v>
+        <v>128</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -5761,32 +5749,32 @@
         <v>29</v>
       </c>
       <c r="M82" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O82" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="P82" t="n">
-        <v>7480.85</v>
+        <v>843154.5699999999</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>FBA79904</t>
+          <t>FBA79444</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>B0FTVQQVDC</t>
+          <t>B0DFMLQBMC</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5796,25 +5784,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>PB-10 (AM-C2+AI-04+AH-60-BL)</t>
+          <t>AM-W20</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>PB-10</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
-        <v>4986.467599999999</v>
+        <v>2164.7070972</v>
       </c>
       <c r="I83" t="n">
-        <v>66</v>
+        <v>6</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -5829,29 +5817,29 @@
         <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O83" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P83" t="n">
-        <v>521422.71</v>
+        <v>12578.82</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>FBA79356</t>
+          <t>FBA79909</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>B0D3Q2T5XX</t>
+          <t>B0FVM17Q4W</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5861,25 +5849,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>AA-19WL</t>
+          <t>AM-W20</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
-        <v>2973.2121576</v>
+        <v>2164.7070972</v>
       </c>
       <c r="I84" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -5891,32 +5879,30 @@
         <v>29</v>
       </c>
       <c r="M84" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="N84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>2</v>
-      </c>
-      <c r="P84" t="n">
-        <v>42147.58</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P84" t="inlineStr"/>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>FBA79833</t>
+          <t>FBA79979</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>B0FJ8PZ9H7</t>
+          <t>B0GN8RQJRG</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5926,25 +5912,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>PB-04 (AI-04 Red + AM-C44 x 2)</t>
+          <t>AK-37-B</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Electric Keyboard</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>PB-04</t>
+          <t>37 Key Electronic Keyboard Black</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
-        <v>7169.514799999999</v>
+        <v>2261.3068296</v>
       </c>
       <c r="I85" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -5959,29 +5945,29 @@
         <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>3</v>
       </c>
       <c r="P85" t="n">
-        <v>121653.73</v>
+        <v>61514.88</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>FBA79839</t>
+          <t>FBA80016</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>B0FQBXS6Y2</t>
+          <t>B0GKPXQ8G3</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5991,25 +5977,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>AH-45 BK</t>
+          <t>AM-W22</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>DJ Headphone</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>DJ Headphone</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
-        <v>614.5220519999999</v>
+        <v>1679.6</v>
       </c>
       <c r="I86" t="n">
-        <v>230</v>
+        <v>34</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -6021,32 +6007,32 @@
         <v>29</v>
       </c>
       <c r="M86" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O86" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="P86" t="n">
-        <v>255484.58</v>
+        <v>84370.52</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>FBA79838</t>
+          <t>FBA78206</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>B0FQBX8J17</t>
+          <t>B0C4YSV3XL</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6056,25 +6042,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>AH-40 SL</t>
+          <t>AM-W15</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>DJ Headphone</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>DJ Headphone</t>
+          <t>Wireless Mic with Charging Case</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
-        <v>477.9615959999999</v>
+        <v>11761.9332</v>
       </c>
       <c r="I87" t="n">
-        <v>185</v>
+        <v>3</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -6089,29 +6075,29 @@
         <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O87" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="P87" t="n">
-        <v>170601.72</v>
+        <v>16505.6</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>FBA79107</t>
+          <t>FBA79845</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>B0CM9P5CCK</t>
+          <t>B0FN7B3KWS</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6121,25 +6107,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>AM-W17</t>
+          <t>UB-02 (AM-S1 + AA-21)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>UB-02</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
-        <v>1043.232336</v>
+        <v>5836.846399999999</v>
       </c>
       <c r="I88" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -6151,32 +6137,32 @@
         <v>29</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N88" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P88" t="n">
-        <v>50913.43</v>
+        <v>263232.76</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>FBA79103</t>
+          <t>FBA80084</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>B0CM6NTWBP</t>
+          <t>B0GXP97CZG</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6186,25 +6172,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>AI-10</t>
+          <t>BE-4</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>Audio Mixer</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>04 channels Mixer</t>
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
-        <v>1499.646483</v>
+        <v>1948.404289679999</v>
       </c>
       <c r="I89" t="n">
-        <v>181</v>
+        <v>7</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -6219,29 +6205,29 @@
         <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="P89" t="n">
-        <v>391501.83</v>
+        <v>22020.17</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>FBA75676</t>
+          <t>FBA79834</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>B0B4DS678Q</t>
+          <t>B0FJ8T4WXM</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6251,25 +6237,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>AM-C4</t>
+          <t>PB-05 (AA-05 + AM-C11 + AI-04)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Tripod</t>
+          <t>PB-05</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
-        <v>1700.734990628047</v>
+        <v>5118.2854</v>
       </c>
       <c r="I90" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -6281,32 +6267,32 @@
         <v>29</v>
       </c>
       <c r="M90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O90" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P90" t="n">
-        <v>14089.43</v>
+        <v>73409.8</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>FBA79821</t>
+          <t>FBA79824</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>B0FJ2JJZL3</t>
+          <t>B0FJ2K95XT</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6316,7 +6302,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>UB-01 (AI-04, AM-S1, AA-21, AM-C2)</t>
+          <t>GB-01 (AM-C43 +AI-10)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -6326,15 +6312,15 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>UB-01</t>
+          <t>GB-01</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
-        <v>9527.5088</v>
+        <v>2585.9936</v>
       </c>
       <c r="I91" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -6346,32 +6332,32 @@
         <v>29</v>
       </c>
       <c r="M91" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O91" t="n">
         <v>1</v>
       </c>
       <c r="P91" t="n">
-        <v>357978.96</v>
+        <v>46140.06</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>FBA78974</t>
+          <t>FBA79841</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>B0CF5RRTDJ</t>
+          <t>B0FQBTRM28</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6381,25 +6367,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>AA-20</t>
+          <t>AH-60-BL</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Headphone</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Headphone</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
-        <v>1107.780080664706</v>
+        <v>1092.483648</v>
       </c>
       <c r="I92" t="n">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -6411,32 +6397,32 @@
         <v>29</v>
       </c>
       <c r="M92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O92" t="n">
         <v>2</v>
       </c>
       <c r="P92" t="n">
-        <v>24455.75</v>
+        <v>83647.21000000001</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>FBA79653</t>
+          <t>FBA79355</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>B0DN6LJZBR</t>
+          <t>B0D3M86SH1</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6446,25 +6432,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>AM-C45 Pro</t>
+          <t>AA-19BL</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
-        <v>2458.088208</v>
+        <v>2973.2121576</v>
       </c>
       <c r="I93" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -6476,32 +6462,32 @@
         <v>29</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N93" t="n">
+        <v>6</v>
+      </c>
+      <c r="O93" t="n">
         <v>2</v>
       </c>
-      <c r="O93" t="n">
-        <v>1</v>
-      </c>
       <c r="P93" t="n">
-        <v>33973.77</v>
+        <v>87904.99000000001</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>FBA79832</t>
+          <t>FBA80002</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>B0FJ8S53GW</t>
+          <t>B0GW96SHSK</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6511,25 +6497,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>GB-05 (AM-C43 + AI-06)</t>
+          <t>AM-W33 Pro</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Wireless Handheld</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>GB-05</t>
+          <t>Single UHF Wireless Microphone With Receiver</t>
         </is>
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
-        <v>3909.104</v>
+        <v>1825.656588</v>
       </c>
       <c r="I94" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -6544,29 +6530,29 @@
         <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>83681.85000000001</v>
+        <v>30197.39</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>FBA80085</t>
+          <t>FBA79972</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>B0GXPBHDRF</t>
+          <t>B0GCP1J2HC</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6576,7 +6562,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>M6</t>
+          <t>M8</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6586,15 +6572,15 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>06 channels Mixer</t>
+          <t>8 channels Mixer</t>
         </is>
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
-        <v>3998.590893</v>
+        <v>4119.760313999999</v>
       </c>
       <c r="I95" t="n">
-        <v>64</v>
+        <v>136</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -6606,32 +6592,32 @@
         <v>29</v>
       </c>
       <c r="M95" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
         <v>0</v>
       </c>
       <c r="O95" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="P95" t="n">
-        <v>346482.53</v>
+        <v>828116.3199999999</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>FBA79847</t>
+          <t>FBA79995</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>B0FN7FYZM3</t>
+          <t>B0GW8VBCBL</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6641,25 +6627,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>PB-09 (AM-C45 + AI-06 + AA-05)</t>
+          <t>AM-C50</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>PB-09</t>
+          <t>Vocal Microphone</t>
         </is>
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
-        <v>4889.153</v>
+        <v>534.6565721999999</v>
       </c>
       <c r="I96" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -6674,29 +6660,29 @@
         <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>39150.73</v>
+        <v>18286.52</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>FBA75680</t>
+          <t>FBA75675</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>B0B4G1PXWV</t>
+          <t>B0B4G8ZB64</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6706,25 +6692,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>AM-C6</t>
+          <t>AM-C3</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Tripod</t>
+          <t>Vocal Microphone</t>
         </is>
       </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
-        <v>1815.59502123</v>
+        <v>659.7098370441175</v>
       </c>
       <c r="I97" t="n">
-        <v>9</v>
+        <v>77</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -6742,26 +6728,26 @@
         <v>6</v>
       </c>
       <c r="O97" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="P97" t="n">
-        <v>12598.26</v>
+        <v>51349.02</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>FBA79448</t>
+          <t>FBA76597</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>B0DFMKY4TT</t>
+          <t>B0BQ7H7418</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6771,25 +6757,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>AM-W35</t>
+          <t>AA-06</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Microphone Wireless Handheld</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Wireless Microphone</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
-        <v>1984.74951924</v>
+        <v>598.3056269558823</v>
       </c>
       <c r="I98" t="n">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -6804,29 +6790,29 @@
         <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O98" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="P98" t="n">
-        <v>54909.83</v>
+        <v>64429.7</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>FBA79815</t>
+          <t>FBA79831</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>B0FPR7VFCH</t>
+          <t>B0FJ8W5Y9Q</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6836,25 +6822,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>AM-W19</t>
+          <t>GB-04 (AM-C45 + AI-06)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>GB-04</t>
         </is>
       </c>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
-        <v>1159.29193338</v>
+        <v>4630.8156</v>
       </c>
       <c r="I99" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -6869,29 +6855,29 @@
         <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>74082.34</v>
+        <v>47190.19</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>FBA79967</t>
+          <t>FBA77171</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>B0G2C2RCXN</t>
+          <t>B0CH4VCD6R</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6901,25 +6887,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>AM-W19</t>
+          <t>AC-6XL</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
-        <v>1159.29193338</v>
+        <v>169.5252546</v>
       </c>
       <c r="I100" t="n">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -6931,30 +6917,32 @@
         <v>29</v>
       </c>
       <c r="M100" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O100" t="n">
-        <v>0</v>
-      </c>
-      <c r="P100" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="P100" t="n">
+        <v>73713.02</v>
+      </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>FBA76863</t>
+          <t>FBA75691</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>B0BPM2T7BQ</t>
+          <t>B0B4G5JG4P</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6964,25 +6952,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>AI-03</t>
+          <t>AM-W14</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>Microphone Wireless Handheld</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>Wireless Microphone</t>
         </is>
       </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
-        <v>2179.9269789525</v>
+        <v>3221.74692</v>
       </c>
       <c r="I101" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -6994,32 +6982,32 @@
         <v>29</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N101" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="O101" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="P101" t="n">
-        <v>152083.17</v>
+        <v>74664.16</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>FBA80016</t>
+          <t>FBA79653</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>B0GKPXQ8G3</t>
+          <t>B0DN6LJZBR</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -7029,25 +7017,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>AM-W22</t>
+          <t>AM-C45 Pro</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
-        <v>1679.6</v>
+        <v>2458.088208</v>
       </c>
       <c r="I102" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -7065,26 +7053,26 @@
         <v>2</v>
       </c>
       <c r="O102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P102" t="n">
-        <v>84370.52</v>
+        <v>33973.77</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>FBA79848</t>
+          <t>FBA79815</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>B0GN97RFPR</t>
+          <t>B0FPR7VFCH</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -7094,25 +7082,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>AM-S2</t>
+          <t>AM-W19</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Monitor Speakers</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Studio Monitor Speaker</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
-        <v>3748.5845172</v>
+        <v>1159.29193338</v>
       </c>
       <c r="I103" t="n">
-        <v>367</v>
+        <v>50</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -7127,29 +7115,29 @@
         <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="O103" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P103" t="n">
-        <v>1893124.28</v>
+        <v>74082.34</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>FBA79106</t>
+          <t>FBA79960</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>B0CM9KJZWQ</t>
+          <t>B0G3B152FR</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -7159,25 +7147,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>AM-C44</t>
+          <t>AM-W47 Wireless</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Voice Amplifier</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dynamic Microphone</t>
+          <t>Wireless Voice Amplifier</t>
         </is>
       </c>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
-        <v>2738.484882</v>
+        <v>920.65253652</v>
       </c>
       <c r="I104" t="n">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -7189,32 +7177,32 @@
         <v>29</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N104" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O104" t="n">
         <v>2</v>
       </c>
       <c r="P104" t="n">
-        <v>119737.23</v>
+        <v>77922.14</v>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>FBA79831</t>
+          <t>FBA79968</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>B0FJ8W5Y9Q</t>
+          <t>B0G53M9258</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -7224,25 +7212,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>GB-04 (AM-C45 + AI-06)</t>
+          <t>AI-14</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Audio Mixer</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>GB-04</t>
+          <t>8 channels Mixer</t>
         </is>
       </c>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
-        <v>4630.8156</v>
+        <v>3065.101673616</v>
       </c>
       <c r="I105" t="n">
-        <v>9</v>
+        <v>93</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -7257,29 +7245,29 @@
         <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P105" t="n">
-        <v>47190.19</v>
+        <v>465048.08</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>FBA75677</t>
+          <t>FBA79005</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>B0B4KC7VBM</t>
+          <t>B0CKHVHVQ1</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -7289,7 +7277,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>AM-C5</t>
+          <t>AM-W45</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -7299,15 +7287,15 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Conference Microphone</t>
+          <t>Wireless Conference Microphone</t>
         </is>
       </c>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
-        <v>1291.959696295941</v>
+        <v>2738.484882</v>
       </c>
       <c r="I106" t="n">
-        <v>87</v>
+        <v>574</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -7322,29 +7310,29 @@
         <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O106" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="P106" t="n">
-        <v>148898.98</v>
+        <v>2197559.03</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>FBA79840</t>
+          <t>FBA79654</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>B0FQBWV1ST</t>
+          <t>B0DN6MNS1X</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -7354,25 +7342,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>AH-60-RD</t>
+          <t>AM-C11 Pro</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Headphone</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Headphone</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
-        <v>1092.483648</v>
+        <v>3140.890488</v>
       </c>
       <c r="I107" t="n">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
@@ -7387,29 +7375,29 @@
         <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="O107" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P107" t="n">
-        <v>57313.83</v>
+        <v>279351.35</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>FBA78961</t>
+          <t>FBA79820</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>B0CBCB9S14</t>
+          <t>B0FQJWWDVK</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7419,25 +7407,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>AM-C40</t>
+          <t>AC-3XL</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Condenser Mic with Boom Arm</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
-        <v>0</v>
+        <v>130.404042</v>
       </c>
       <c r="I108" t="n">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -7449,32 +7437,32 @@
         <v>29</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N108" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="O108" t="n">
         <v>1</v>
       </c>
       <c r="P108" t="n">
-        <v>4243.48</v>
+        <v>17099.41</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>FBA76721</t>
+          <t>FBA78204</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>B0BLKB55BM</t>
+          <t>B0C4YT43Z3</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7484,25 +7472,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>AM-C18</t>
+          <t>AM-C31</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Microphone dynamic</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mobile Microphone</t>
+          <t>USB Microphone Kit - Tripod</t>
         </is>
       </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
-        <v>2664.193308210882</v>
+        <v>3835.413</v>
       </c>
       <c r="I109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -7522,24 +7510,22 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
-      <c r="P109" t="n">
-        <v>1683.78</v>
-      </c>
+      <c r="P109" t="inlineStr"/>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>FBA75673</t>
+          <t>FBA75679</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>B0B4DPX2J2</t>
+          <t>B0B4JRQP22</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7549,25 +7535,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>AM-C1</t>
+          <t>AA-02</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Boomarm</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
-        <v>1475.964687829412</v>
+        <v>1330.281037275</v>
       </c>
       <c r="I110" t="n">
-        <v>2485</v>
+        <v>153</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -7579,32 +7565,32 @@
         <v>29</v>
       </c>
       <c r="M110" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N110" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
-        <v>194</v>
+        <v>6</v>
       </c>
       <c r="P110" t="n">
-        <v>4735410.53</v>
+        <v>259341.18</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>FBA78976</t>
+          <t>FBA79967</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>B0CF5SHL15</t>
+          <t>B0G2C2RCXN</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7614,25 +7600,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>AA-22</t>
+          <t>AM-W19</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Monitor Speakers Accessories</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Monitor Speaker Stand Pair</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
-        <v>1722.835557825</v>
+        <v>1159.29193338</v>
       </c>
       <c r="I111" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
@@ -7644,32 +7630,30 @@
         <v>29</v>
       </c>
       <c r="M111" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="N111" t="n">
         <v>0</v>
       </c>
       <c r="O111" t="n">
-        <v>5</v>
-      </c>
-      <c r="P111" t="n">
-        <v>60943.01</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P111" t="inlineStr"/>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>FBA76723</t>
+          <t>FBA75683</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>B0BLKF46QG</t>
+          <t>B0B4G94VP3</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7679,25 +7663,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>AM-C20</t>
+          <t>AA-03</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Tripod</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
-        <v>1235.473403164659</v>
+        <v>179.9635942941177</v>
       </c>
       <c r="I112" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -7709,32 +7693,32 @@
         <v>29</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N112" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P112" t="n">
-        <v>3729.48</v>
+        <v>17526.55</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>FBA79959</t>
+          <t>FBA80085</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>B0G39ZHDYP</t>
+          <t>B0GXPBHDRF</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7744,25 +7728,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>AM-W47 Wired</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Voice Amplifier</t>
+          <t>Audio Mixer</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Wired Voice Amplifier</t>
+          <t>06 channels Mixer</t>
         </is>
       </c>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
-        <v>503.35960212</v>
+        <v>3998.590893</v>
       </c>
       <c r="I113" t="n">
-        <v>127</v>
+        <v>65</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -7774,32 +7758,32 @@
         <v>29</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="N113" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P113" t="n">
-        <v>121816.59</v>
+        <v>351516.12</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>FBA79104</t>
+          <t>FBA79655</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>B0CM6NVLT9</t>
+          <t>B0DN6PFWNK</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7809,25 +7793,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>AI-11</t>
+          <t>AM-C44 Pro</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
-        <v>847.6262729999999</v>
+        <v>3277.450944</v>
       </c>
       <c r="I114" t="n">
-        <v>159</v>
+        <v>26</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -7842,29 +7826,29 @@
         <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="O114" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="P114" t="n">
-        <v>172055.34</v>
+        <v>100388.06</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>FBA79909</t>
+          <t>FBA75674</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>B0FVM17Q4W</t>
+          <t>B0B4G19R58</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7874,25 +7858,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>AM-W20</t>
+          <t>AM-C2</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>XLR Microphone Kit - Boomarm</t>
         </is>
       </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
-        <v>2164.7070972</v>
+        <v>2119.874127397059</v>
       </c>
       <c r="I115" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -7904,30 +7888,32 @@
         <v>29</v>
       </c>
       <c r="M115" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O115" t="n">
-        <v>0</v>
-      </c>
-      <c r="P115" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="P115" t="n">
+        <v>267173.45</v>
+      </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>FBA79823</t>
+          <t>FBA76723</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>B0FJ2HZCVN</t>
+          <t>B0BLKF46QG</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7937,25 +7923,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>PB-01 (AM-C11 + AI-04)</t>
+          <t>AM-C20</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>PB-01</t>
+          <t>USB Microphone Kit - Tripod</t>
         </is>
       </c>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
-        <v>4859.948</v>
+        <v>1235.473403164659</v>
       </c>
       <c r="I116" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -7970,29 +7956,29 @@
         <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="O116" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P116" t="n">
-        <v>82498.16</v>
+        <v>3729.48</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>FBA79825</t>
+          <t>FBA79445</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>B0FJ2DT13L</t>
+          <t>B0DFMLS8JG</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -8002,25 +7988,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>GB-02 (AM-C43 + AI-11)</t>
+          <t>AM-W32</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Wireless Handheld</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>GB-02</t>
+          <t>Wireless Microphone</t>
         </is>
       </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
-        <v>1983.58</v>
+        <v>2167.31517804</v>
       </c>
       <c r="I117" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -8038,26 +8024,26 @@
         <v>1</v>
       </c>
       <c r="O117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P117" t="n">
-        <v>66129.73</v>
+        <v>71574.49000000001</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>FBA79969</t>
+          <t>FBA79961</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>B0G3B677Z5</t>
+          <t>B0G53H49BS</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -8067,25 +8053,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>UB-03 (AM-S1 + AA-22)</t>
+          <t>AI-13</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Audio Mixer</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>UB-03</t>
+          <t>4 channels Mixer</t>
         </is>
       </c>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
-        <v>5619.632</v>
+        <v>1544.91011775</v>
       </c>
       <c r="I118" t="n">
-        <v>18</v>
+        <v>454</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -8097,32 +8083,32 @@
         <v>29</v>
       </c>
       <c r="M118" t="n">
-        <v>6</v>
+        <v>69</v>
       </c>
       <c r="N118" t="n">
         <v>0</v>
       </c>
       <c r="O118" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="P118" t="n">
-        <v>163601.96</v>
+        <v>962394.0600000001</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>FBA75684</t>
+          <t>FBA79904</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>B0B4G7VWXD</t>
+          <t>B0FTVQQVDC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -8132,22 +8118,22 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>AA-04</t>
+          <t>PB-10 (AM-C2+AI-04+AH-60-BL)</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>PB-10</t>
         </is>
       </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
-        <v>871.9473036705882</v>
+        <v>4986.467599999999</v>
       </c>
       <c r="I119" t="n">
         <v>66</v>
@@ -8162,32 +8148,32 @@
         <v>29</v>
       </c>
       <c r="M119" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="P119" t="n">
-        <v>74884.23</v>
+        <v>521422.71</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>FBA76728</t>
+          <t>FBA76730</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>B0BLNCP74M</t>
+          <t>B0BLKB6FRR</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -8197,25 +8183,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>AM-C25</t>
+          <t>AM-C27</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Boomarm</t>
+          <t>Vocal Microphone</t>
         </is>
       </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
-        <v>2157.615343358823</v>
+        <v>827.5708984229998</v>
       </c>
       <c r="I120" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -8227,32 +8213,32 @@
         <v>29</v>
       </c>
       <c r="M120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
       </c>
       <c r="P120" t="n">
-        <v>1626.51</v>
+        <v>3021.51</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>FBA79108</t>
+          <t>FBA79447</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>B0CM9L1QZG</t>
+          <t>B0DFMLXD9S</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -8262,25 +8248,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>AM-W16</t>
+          <t>AM-W34</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Microphone Wireless Handheld</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>Wireless Microphone</t>
         </is>
       </c>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
-        <v>756.3434436</v>
+        <v>2360.3131602</v>
       </c>
       <c r="I121" t="n">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
@@ -8292,32 +8278,32 @@
         <v>29</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N121" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="O121" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P121" t="n">
-        <v>46924.36</v>
+        <v>31526.62</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>FBA79995</t>
+          <t>FBA76727</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>B0GW8VBCBL</t>
+          <t>B0BLKCDRNB</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -8327,25 +8313,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>AM-C50</t>
+          <t>AM-C24</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vocal Microphone</t>
+          <t>USB Microphone Kit - Tripod</t>
         </is>
       </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
-        <v>534.6565721999999</v>
+        <v>1676.644024574118</v>
       </c>
       <c r="I122" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
@@ -8357,32 +8343,32 @@
         <v>29</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N122" t="n">
         <v>0</v>
       </c>
       <c r="O122" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P122" t="n">
-        <v>18286.52</v>
+        <v>0</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>FBA79008</t>
+          <t>FBA79813</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>B0CH4RT4P8</t>
+          <t>B0FG88HVQ8</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -8392,25 +8378,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>AI-06</t>
+          <t>AH-50</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>DJ Headphone</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>DJ Headphone</t>
         </is>
       </c>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
-        <v>2934.090945</v>
+        <v>1201.7320128</v>
       </c>
       <c r="I123" t="n">
-        <v>14</v>
+        <v>542</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -8425,29 +8411,29 @@
         <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="O123" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="P123" t="n">
-        <v>35964.5</v>
+        <v>803052.7</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>FBA75687</t>
+          <t>FBA79356</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>B0B4G5ZLTB</t>
+          <t>B0D3Q2T5XX</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8457,25 +8443,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>AM-W11</t>
+          <t>AA-19WL</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Wireless Microphone</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
-        <v>2857.758705882353</v>
+        <v>2973.2121576</v>
       </c>
       <c r="I124" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
@@ -8487,32 +8473,32 @@
         <v>29</v>
       </c>
       <c r="M124" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O124" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P124" t="n">
-        <v>1885.92</v>
+        <v>32233.45</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>FBA79972</t>
+          <t>FBA75680</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>B0GCP1J2HC</t>
+          <t>B0B4G1PXWV</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8522,25 +8508,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>AM-C6</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Audio Mixer</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>8 channels Mixer</t>
+          <t>USB Microphone Kit - Tripod</t>
         </is>
       </c>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
-        <v>4119.760313999999</v>
+        <v>1815.59502123</v>
       </c>
       <c r="I125" t="n">
-        <v>116</v>
+        <v>9</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -8552,32 +8538,32 @@
         <v>29</v>
       </c>
       <c r="M125" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O125" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="P125" t="n">
-        <v>705069.8</v>
+        <v>12598.26</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>FBA79009</t>
+          <t>FBA79980</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>B0CH4PMR8K</t>
+          <t>B0GN8MMKY1</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8587,25 +8573,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>AM-C41</t>
+          <t>AK-37-W</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Electric Keyboard</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Tripod</t>
+          <t>37 Key Electronic Keyboard White</t>
         </is>
       </c>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
-        <v>1043.232336</v>
+        <v>2335.8554064</v>
       </c>
       <c r="I126" t="n">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
@@ -8620,29 +8606,29 @@
         <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O126" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P126" t="n">
-        <v>54842.96</v>
+        <v>13980.65</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>FBA76414</t>
+          <t>FBA79449</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>B0BLJVJ2GN</t>
+          <t>B0DFMNGFTD</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8652,25 +8638,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>AA-05</t>
+          <t>AM-W36</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Microphone Wireless Handheld</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Wireless Microphone</t>
         </is>
       </c>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
-        <v>280.0829144294117</v>
+        <v>4042.525302</v>
       </c>
       <c r="I127" t="n">
-        <v>591</v>
+        <v>18</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
@@ -8682,32 +8668,32 @@
         <v>29</v>
       </c>
       <c r="M127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="O127" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="P127" t="n">
-        <v>275741.01</v>
+        <v>80319.42999999999</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>FBA79816</t>
+          <t>FBA79107</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>B0FPR962YS</t>
+          <t>B0CM9P5CCK</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8717,7 +8703,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>AM-W22</t>
+          <t>AM-W17</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -8732,10 +8718,10 @@
       </c>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
-        <v>1679.60406096</v>
+        <v>1043.232336</v>
       </c>
       <c r="I128" t="n">
-        <v>173</v>
+        <v>37</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
@@ -8750,29 +8736,29 @@
         <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>164</v>
+        <v>35</v>
       </c>
       <c r="O128" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P128" t="n">
-        <v>435345.64</v>
+        <v>52327.7</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>FBA75675</t>
+          <t>FBA79963</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>B0B4G8ZB64</t>
+          <t>B0G53CB72D</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8782,25 +8768,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>AM-C3</t>
+          <t>AM-Pro8</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Audio Mixer</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vocal Microphone</t>
+          <t>8 channels Mixer</t>
         </is>
       </c>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
-        <v>659.7098370441175</v>
+        <v>12112.09532316</v>
       </c>
       <c r="I129" t="n">
-        <v>78</v>
+        <v>3</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
@@ -8815,29 +8801,29 @@
         <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O129" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="P129" t="n">
-        <v>52020.25</v>
+        <v>47194.42</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>FBA80084</t>
+          <t>FBA76862</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>B0GXP97CZG</t>
+          <t>B0BPLWW72Y</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8847,25 +8833,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>BE-4</t>
+          <t>AM-C28</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Audio Mixer</t>
+          <t>Microphone Conference</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>04 channels Mixer</t>
+          <t>Conference Microphone</t>
         </is>
       </c>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
-        <v>1948.404289679999</v>
+        <v>874.2436631991176</v>
       </c>
       <c r="I130" t="n">
-        <v>7</v>
+        <v>177</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
@@ -8880,29 +8866,29 @@
         <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O130" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="P130" t="n">
-        <v>22020.17</v>
+        <v>210581.01</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>FBA79708</t>
+          <t>FBA80009</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>B0FFB6YJM1</t>
+          <t>B0GW8R2RYM</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8912,25 +8898,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>SB-01</t>
+          <t>AM-C51</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Sound Bar</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Sound Bar</t>
+          <t>Vocal Microphone</t>
         </is>
       </c>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
-        <v>708</v>
+        <v>912.8282939999998</v>
       </c>
       <c r="I131" t="n">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
@@ -8942,32 +8928,32 @@
         <v>29</v>
       </c>
       <c r="M131" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
         <v>0</v>
       </c>
       <c r="O131" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="P131" t="n">
-        <v>166898.32</v>
+        <v>18687.28</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>FBA76722</t>
+          <t>FBA76414</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>B0BLKDC4PP</t>
+          <t>B0BLJVJ2GN</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8977,25 +8963,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>AM-C19</t>
+          <t>AA-05</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Tripod</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
-        <v>1642.572937873306</v>
+        <v>280.0829144294117</v>
       </c>
       <c r="I132" t="n">
-        <v>0</v>
+        <v>589</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
@@ -9007,30 +8993,32 @@
         <v>29</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="O132" t="n">
-        <v>0</v>
-      </c>
-      <c r="P132" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="P132" t="n">
+        <v>274807.88</v>
+      </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>FBA79654</t>
+          <t>FBA76725</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>B0DN6MNS1X</t>
+          <t>B0BLKCSJ7Z</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -9040,25 +9028,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>AM-C11 Pro</t>
+          <t>AM-C22</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>USB Microphone Kit - Tripod</t>
         </is>
       </c>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="n">
-        <v>3140.890488</v>
+        <v>849.3751611646587</v>
       </c>
       <c r="I133" t="n">
-        <v>75</v>
+        <v>3</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -9073,29 +9061,29 @@
         <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>75</v>
+        <v>3</v>
       </c>
       <c r="O133" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P133" t="n">
-        <v>283126.37</v>
+        <v>0</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>FBA79379</t>
+          <t>FBA79105</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>B0D3LZWTHV</t>
+          <t>B0CM6WH4ZT</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -9105,25 +9093,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>AM-C45</t>
+          <t>AI-12</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dynamic Microphone</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
-        <v>2021.262651</v>
+        <v>678.1010183999999</v>
       </c>
       <c r="I134" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
@@ -9135,32 +9123,32 @@
         <v>29</v>
       </c>
       <c r="M134" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N134" t="n">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="O134" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P134" t="n">
-        <v>77066.7</v>
+        <v>94324.98</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>FBA78973</t>
+          <t>FBA76722</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>B0CF5R3V95</t>
+          <t>B0BLKDC4PP</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -9170,25 +9158,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>AA-19</t>
+          <t>AM-C19</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>USB Microphone Kit - Tripod</t>
         </is>
       </c>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="n">
-        <v>1960.237563966397</v>
+        <v>1642.572937873306</v>
       </c>
       <c r="I135" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
@@ -9200,32 +9188,30 @@
         <v>29</v>
       </c>
       <c r="M135" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N135" t="n">
         <v>0</v>
       </c>
       <c r="O135" t="n">
-        <v>8</v>
-      </c>
-      <c r="P135" t="n">
-        <v>325358.18</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P135" t="inlineStr"/>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>FBA80002</t>
+          <t>FBA79840</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>B0GW96SHSK</t>
+          <t>B0FQBWV1ST</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -9235,25 +9221,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>AM-W33 Pro</t>
+          <t>AH-60-RD</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Microphone Wireless Handheld</t>
+          <t>Headphone</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Single UHF Wireless Microphone With Receiver</t>
+          <t>Headphone</t>
         </is>
       </c>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
-        <v>1825.656588</v>
+        <v>1092.483648</v>
       </c>
       <c r="I136" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
@@ -9271,26 +9257,26 @@
         <v>0</v>
       </c>
       <c r="O136" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P136" t="n">
-        <v>30197.39</v>
+        <v>52666.76</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>FBA80003</t>
+          <t>FBA79448</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>B0GW92TTMS</t>
+          <t>B0DFMKY4TT</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -9300,7 +9286,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>AM-W32 Pro</t>
+          <t>AM-W35</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -9310,15 +9296,15 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Dual UHF Wireless Microphone With Receiver</t>
+          <t>Wireless Microphone</t>
         </is>
       </c>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
-        <v>3129.697008</v>
+        <v>1984.74951924</v>
       </c>
       <c r="I137" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
@@ -9333,29 +9319,29 @@
         <v>0</v>
       </c>
       <c r="N137" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P137" t="n">
-        <v>61869.39</v>
+        <v>57775.88</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>FBA79842</t>
+          <t>FBA76721</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>B0G4DNF8RZ</t>
+          <t>B0BLKB55BM</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -9365,25 +9351,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>AM-C48</t>
+          <t>AM-C18</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Microphone dynamic</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Mobile Microphone</t>
         </is>
       </c>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="n">
-        <v>1956.06063</v>
+        <v>2664.193308210882</v>
       </c>
       <c r="I138" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
@@ -9395,32 +9381,32 @@
         <v>29</v>
       </c>
       <c r="M138" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N138" t="n">
         <v>0</v>
       </c>
       <c r="O138" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P138" t="n">
-        <v>126732.34</v>
+        <v>1683.78</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>FBA79841</t>
+          <t>FBA75673</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>B0FQBTRM28</t>
+          <t>B0B4DPX2J2</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -9430,25 +9416,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>AH-60-BL</t>
+          <t>AM-C1</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Headphone</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Headphone</t>
+          <t>USB Microphone Kit - Boomarm</t>
         </is>
       </c>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
-        <v>1092.483648</v>
+        <v>1475.964687829412</v>
       </c>
       <c r="I139" t="n">
-        <v>54</v>
+        <v>2480</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
@@ -9460,32 +9446,32 @@
         <v>29</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N139" t="n">
-        <v>1</v>
+        <v>205</v>
       </c>
       <c r="O139" t="n">
-        <v>3</v>
+        <v>197</v>
       </c>
       <c r="P139" t="n">
-        <v>83647.21000000001</v>
+        <v>4726055.07</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>FBA79963</t>
+          <t>FBA79008</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>B0G53CB72D</t>
+          <t>B0CH4RT4P8</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -9495,25 +9481,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>AM-Pro8</t>
+          <t>AI-06</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Audio Mixer</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>8 channels Mixer</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
-        <v>12112.09532316</v>
+        <v>2934.090945</v>
       </c>
       <c r="I140" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
@@ -9528,29 +9514,29 @@
         <v>0</v>
       </c>
       <c r="N140" t="n">
+        <v>14</v>
+      </c>
+      <c r="O140" t="n">
         <v>1</v>
       </c>
-      <c r="O140" t="n">
-        <v>0</v>
-      </c>
       <c r="P140" t="n">
-        <v>47194.42</v>
+        <v>35964.5</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>FBA80004</t>
+          <t>FBA79832</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>B0GW92316G</t>
+          <t>B0FJ8S53GW</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9560,25 +9546,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>AM-W36 Pro</t>
+          <t>GB-05 (AM-C43 + AI-06)</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Microphone Wireless Handheld</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Dual UHF Wireless Microphone With Receiver Box</t>
+          <t>GB-05</t>
         </is>
       </c>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="n">
-        <v>4694.545512</v>
+        <v>3909.104</v>
       </c>
       <c r="I141" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
@@ -9593,17 +9579,82 @@
         <v>0</v>
       </c>
       <c r="N141" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P141" t="n">
-        <v>106966.25</v>
+        <v>83681.85000000001</v>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>FBA75684</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>B0B4G7VWXD</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>AA-04</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Microphone Accessories</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="n">
+        <v>871.9473036705882</v>
+      </c>
+      <c r="I142" t="n">
+        <v>66</v>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>1p</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="n">
+        <v>29</v>
+      </c>
+      <c r="M142" t="n">
+        <v>5</v>
+      </c>
+      <c r="N142" t="n">
+        <v>5</v>
+      </c>
+      <c r="O142" t="n">
+        <v>15</v>
+      </c>
+      <c r="P142" t="n">
+        <v>74884.23</v>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>

--- a/data/raw/inventory/Week 29/Audio_Array/Vendor SOH (SP-API).xlsx
+++ b/data/raw/inventory/Week 29/Audio_Array/Vendor SOH (SP-API).xlsx
@@ -506,12 +506,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FBA79982</t>
+          <t>FBA79654</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>B0GN8MPYPG</t>
+          <t>B0DN6MNS1X</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -521,25 +521,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AK-61 Pro</t>
+          <t>AM-C11 Pro</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Electric Keyboard</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61 Key Electronic Keyboard With LCD DIsplay</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>3317.4116676</v>
+        <v>3140.890488</v>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -551,16 +551,16 @@
         <v>29</v>
       </c>
       <c r="M2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="O2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="P2" t="n">
-        <v>26914.61</v>
+        <v>279351.35</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -571,12 +571,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FBA79846</t>
+          <t>FBA79482</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>B0FN7C25VS</t>
+          <t>B0DXFPM4N2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -586,25 +586,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AM-C11X Pro</t>
+          <t>AM-S1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Monitor Speakers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Studio Monitor Speaker</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>2263.0394</v>
+        <v>4486.010979600001</v>
       </c>
       <c r="I3" t="n">
-        <v>11</v>
+        <v>128</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -616,16 +616,16 @@
         <v>29</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="P3" t="n">
-        <v>36141.32</v>
+        <v>843154.5699999999</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FBA79823</t>
+          <t>FBA79815</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>B0FJ2HZCVN</t>
+          <t>B0FPR7VFCH</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -651,25 +651,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PB-01 (AM-C11 + AI-04)</t>
+          <t>AM-W19</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PB-01</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>4859.948</v>
+        <v>1159.29193338</v>
       </c>
       <c r="I4" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -684,13 +684,13 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>82498.16</v>
+        <v>74082.34</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -701,12 +701,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FBA79104</t>
+          <t>FBA79448</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>B0CM6NVLT9</t>
+          <t>B0DFMKY4TT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -716,25 +716,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AI-11</t>
+          <t>AM-W35</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>Microphone Wireless Handheld</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>Wireless Microphone</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>847.6262729999999</v>
+        <v>1984.74951924</v>
       </c>
       <c r="I5" t="n">
-        <v>151</v>
+        <v>21</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -749,13 +749,13 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>163390.09</v>
+        <v>57775.88</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -766,12 +766,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FBA76864</t>
+          <t>FBA79960</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0G3B152FR</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -781,25 +781,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AI-04 Red</t>
+          <t>AM-W47 Wireless</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>Voice Amplifier</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>Wireless Voice Amplifier</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>2165.574481998618</v>
+        <v>920.65253652</v>
       </c>
       <c r="I6" t="n">
-        <v>870</v>
+        <v>51</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -811,16 +811,16 @@
         <v>29</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O6" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>3077071.27</v>
+        <v>77922.14</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -831,12 +831,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FBA79908</t>
+          <t>FBA79968</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>B0FTVV1QJY</t>
+          <t>B0G53M9258</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -846,25 +846,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>PB-14 (AM-C43+AH-40-SL+AI-12)</t>
+          <t>AI-14</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Audio Mixer</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PB-14</t>
+          <t>8 channels Mixer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>2280.5034</v>
+        <v>3065.101673616</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>93</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -876,16 +876,16 @@
         <v>29</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P7" t="n">
-        <v>16218.84</v>
+        <v>465048.08</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -896,12 +896,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FBA79822</t>
+          <t>FBA79836</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B0FJ2J6MTF</t>
+          <t>B0FJ8Z1W81</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>KB-01 (AM-W32 + AI-12)</t>
+          <t>PB-07 (AA-05 + AM-C45 + AI-04)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -921,15 +921,15 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>KB-01</t>
+          <t>PB-07</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>2630.5268</v>
+        <v>4180.2798</v>
       </c>
       <c r="I8" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -941,16 +941,16 @@
         <v>29</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>99409.85000000001</v>
+        <v>81238.77</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -961,12 +961,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FBA78424</t>
+          <t>FBA79694</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>B0C55MY66L</t>
+          <t>B0DT6T6N6B</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -976,25 +976,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>AM-C37</t>
+          <t>AA-26</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USB/XLR Dynamic Mic</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>3103.426797881559</v>
+        <v>260.808084</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>381</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1006,16 +1006,16 @@
         <v>29</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>157302.05</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1026,12 +1026,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FBA79380</t>
+          <t>FBA79840</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>B0D3M1B4Z8</t>
+          <t>B0FQBWV1ST</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1041,25 +1041,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>AM-C46</t>
+          <t>AH-60-RD</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Headphone</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Condenser Mic with Boom Arm</t>
+          <t>Headphone</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>2021.262651</v>
+        <v>1092.483648</v>
       </c>
       <c r="I10" t="n">
-        <v>298</v>
+        <v>34</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1074,13 +1074,13 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>792266.62</v>
+        <v>52666.76</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1091,12 +1091,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FBA79906</t>
+          <t>FBA76723</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>B0FTVVLNS9</t>
+          <t>B0BLKF46QG</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1106,25 +1106,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>PB-12 (AM-C11+AA-05+AI-04+AH-60-RD)</t>
+          <t>AM-C20</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PB-12</t>
+          <t>USB Microphone Kit - Tripod</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>6152.0362</v>
+        <v>1235.473403164659</v>
       </c>
       <c r="I11" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1136,16 +1136,16 @@
         <v>29</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>211423.58</v>
+        <v>3729.48</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1156,12 +1156,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FBA79847</t>
+          <t>FBA79907</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>B0FN7FYZM3</t>
+          <t>B0FTVS34SD</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>PB-09 (AM-C45 + AI-06 + AA-05)</t>
+          <t>PB-13 (AM-C43+AH-40-SL+AI-11)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1181,15 +1181,15 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PB-09</t>
+          <t>PB-13</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>4889.153</v>
+        <v>2436.8652</v>
       </c>
       <c r="I12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1204,14 +1204,12 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="P12" t="n">
-        <v>39150.73</v>
-      </c>
+      <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr">
         <is>
           <t>2026-07-18</t>
@@ -1221,12 +1219,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FBA79981</t>
+          <t>FBA80016</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>B0GN8MFDGZ</t>
+          <t>B0GKPXQ8G3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1236,25 +1234,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>AK-61 Neo</t>
+          <t>AM-W22</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Electric Keyboard</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61 Key Electronic Keyboard With LED DIsplay</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>2870.1202068</v>
+        <v>1679.6</v>
       </c>
       <c r="I13" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1269,13 +1267,13 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O13" t="n">
         <v>2</v>
       </c>
       <c r="P13" t="n">
-        <v>45439.37</v>
+        <v>84370.52</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -1286,12 +1284,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FBA75692</t>
+          <t>FBA79708</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>B0B4G1HPL5</t>
+          <t>B0FFB6YJM1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1301,25 +1299,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>AM-C11</t>
+          <t>SB-01</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Sound Bar</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USB/XLR Dynamic Mic</t>
+          <t>Sound Bar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>2975.579697881559</v>
+        <v>708</v>
       </c>
       <c r="I14" t="n">
-        <v>25</v>
+        <v>172</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1331,16 +1329,16 @@
         <v>29</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="N14" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="P14" t="n">
-        <v>89131.53999999999</v>
+        <v>164979.95</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -1351,12 +1349,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FBA80003</t>
+          <t>FBA79104</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>B0GW92TTMS</t>
+          <t>B0CM6NVLT9</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1366,25 +1364,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>AM-W32 Pro</t>
+          <t>AI-11</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Microphone Wireless Handheld</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dual UHF Wireless Microphone With Receiver</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>3129.697008</v>
+        <v>847.6262729999999</v>
       </c>
       <c r="I15" t="n">
-        <v>15</v>
+        <v>151</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1399,13 +1397,13 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="P15" t="n">
-        <v>61869.39</v>
+        <v>163390.09</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -1416,12 +1414,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FBA78976</t>
+          <t>FBA79445</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>B0CF5SHL15</t>
+          <t>B0DFMLS8JG</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1431,25 +1429,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>AA-22</t>
+          <t>AM-W32</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Monitor Speakers Accessories</t>
+          <t>Microphone Wireless Handheld</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Monitor Speaker Stand Pair</t>
+          <t>Wireless Microphone</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>1722.835557825</v>
+        <v>2167.31517804</v>
       </c>
       <c r="I16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1461,16 +1459,16 @@
         <v>29</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P16" t="n">
-        <v>66026.89999999999</v>
+        <v>71574.49000000001</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -1481,12 +1479,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FBA79965</t>
+          <t>FBA79655</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>B0G53PRM34</t>
+          <t>B0DN6PFWNK</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1496,25 +1494,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>AM-Mix6</t>
+          <t>AM-C44 Pro</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Audio Mixer</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>6 channels mixer</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>4696.526757959999</v>
+        <v>3277.450944</v>
       </c>
       <c r="I17" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1526,16 +1524,16 @@
         <v>29</v>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P17" t="n">
-        <v>59775.97</v>
+        <v>100388.06</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -1546,12 +1544,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FBA80007</t>
+          <t>FBA79826</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>B0GN2LHJY4</t>
+          <t>B0FJ2LQT7K</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1561,25 +1559,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>MT-12</t>
+          <t>PB-02 (AI-04 Red + AM-C11 + AA-05)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Audio Mixer</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>12 channels Mixer</t>
+          <t>PB-02</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>4119.760313999999</v>
+        <v>5118.2854</v>
       </c>
       <c r="I18" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1591,16 +1589,16 @@
         <v>29</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="O18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>74737.64999999999</v>
+        <v>120811.9</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -1611,12 +1609,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FBA79833</t>
+          <t>FBA79841</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>B0FJ8PZ9H7</t>
+          <t>B0FQBTRM28</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1626,25 +1624,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>PB-04 (AI-04 Red + AM-C44 x 2)</t>
+          <t>AH-60-BL</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Headphone</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>PB-04</t>
+          <t>Headphone</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>7169.514799999999</v>
+        <v>1092.483648</v>
       </c>
       <c r="I19" t="n">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1659,13 +1657,13 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P19" t="n">
-        <v>121653.73</v>
+        <v>83647.21000000001</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -1676,12 +1674,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FBA75678</t>
+          <t>FBA79965</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>B0B4G8PH2P</t>
+          <t>B0G53PRM34</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1691,25 +1689,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>AA-01</t>
+          <t>AM-Mix6</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Audio Mixer</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>6 channels mixer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>1224.499030661912</v>
+        <v>4696.526757959999</v>
       </c>
       <c r="I20" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1721,16 +1719,16 @@
         <v>29</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>48433.97</v>
+        <v>59775.97</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -1741,12 +1739,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FBA79826</t>
+          <t>FBA76730</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>B0FJ2LQT7K</t>
+          <t>B0BLKB6FRR</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1756,25 +1754,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>PB-02 (AI-04 Red + AM-C11 + AA-05)</t>
+          <t>AM-C27</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PB-02</t>
+          <t>Vocal Microphone</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>5118.2854</v>
+        <v>827.5708984229998</v>
       </c>
       <c r="I21" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1789,13 +1787,13 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>120811.9</v>
+        <v>3021.51</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -1806,12 +1804,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FBA79966</t>
+          <t>FBA79447</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>B0G53KWRVW</t>
+          <t>B0DFMLXD9S</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1821,25 +1819,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>AM-Mix10</t>
+          <t>AM-W34</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Audio Mixer</t>
+          <t>Microphone Wireless Handheld</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>10 channels mixer</t>
+          <t>Wireless Microphone</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>5808.86204274</v>
+        <v>2360.3131602</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1851,16 +1849,16 @@
         <v>29</v>
       </c>
       <c r="M22" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O22" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>31526.62</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -1871,12 +1869,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FBA79230</t>
+          <t>FBA78961</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>B0CX1XK5R6</t>
+          <t>B0CBCB9S14</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1886,25 +1884,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>AM-W46</t>
+          <t>AM-C40</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Speaker Karaoke</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Microphone with Speaker</t>
+          <t>Condenser Mic with Boom Arm</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>4277.252577599999</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1919,13 +1917,13 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P23" t="n">
-        <v>18315.74</v>
+        <v>4243.48</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -1936,12 +1934,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FBA79446</t>
+          <t>FBA77171</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>B0DFMMTWLY</t>
+          <t>B0CH4VCD6R</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1951,25 +1949,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>AM-W33</t>
+          <t>AC-6XL</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Microphone Wireless Handheld</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Wireless Microphone</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>1194.50102472</v>
+        <v>169.5252546</v>
       </c>
       <c r="I24" t="n">
-        <v>36</v>
+        <v>179</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1981,16 +1979,16 @@
         <v>29</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O24" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P24" t="n">
-        <v>53069.79</v>
+        <v>73713.02</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -2001,12 +1999,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FBA79905</t>
+          <t>FBA79827</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>B0FTVSH458</t>
+          <t>B0FJ8S5XJ8</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2016,7 +2014,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>PB-11 (AM-C44+AA-05+AH-45-BK)</t>
+          <t>PB-03 (AI-04 Red + AM-C11 x 2)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2026,15 +2024,15 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>PB-11</t>
+          <t>PB-03</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>3425.8468</v>
+        <v>7722.439199999999</v>
       </c>
       <c r="I25" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2049,13 +2047,13 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>25797.25</v>
+        <v>155003.82</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -2066,12 +2064,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FBA75688</t>
+          <t>FBA75677</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>B0B4G763WS</t>
+          <t>B0B4KC7VBM</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2081,25 +2079,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>AM-W12</t>
+          <t>AM-C5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Microphone Wireless Handheld</t>
+          <t>Microphone Conference</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wireless Microphone</t>
+          <t>Conference Microphone</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>1956.963080117647</v>
+        <v>1291.959696295941</v>
       </c>
       <c r="I26" t="n">
-        <v>11</v>
+        <v>80</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2111,16 +2109,16 @@
         <v>29</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P26" t="n">
-        <v>32295.69</v>
+        <v>136640.87</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -2131,12 +2129,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FBA75687</t>
+          <t>FBA79107</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>B0B4G5ZLTB</t>
+          <t>B0CM9P5CCK</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2146,7 +2144,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>AM-W11</t>
+          <t>AM-W17</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2156,15 +2154,15 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Wireless Microphone</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>2857.758705882353</v>
+        <v>1043.232336</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2176,16 +2174,16 @@
         <v>29</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="O27" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P27" t="n">
-        <v>1885.92</v>
+        <v>52327.7</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -2196,12 +2194,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FBA78925</t>
+          <t>FBA79109</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>B0CBC7QMNV</t>
+          <t>B0CM9HYVDM</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2211,25 +2209,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>AM-C11X</t>
+          <t>AM-W18</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Speaker Karaoke</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>XLR Dynamic Mic</t>
+          <t>Microphone with Speaker</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>2173.4007</v>
+        <v>612.8989974</v>
       </c>
       <c r="I28" t="n">
-        <v>19</v>
+        <v>235</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2241,16 +2239,16 @@
         <v>29</v>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
+        <v>43</v>
+      </c>
+      <c r="O28" t="n">
         <v>3</v>
       </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
       <c r="P28" t="n">
-        <v>51861.01</v>
+        <v>205107.74</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -2261,12 +2259,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FBA79009</t>
+          <t>FBA80009</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>B0CH4PMR8K</t>
+          <t>B0GW8R2RYM</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2276,25 +2274,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>AM-C41</t>
+          <t>AM-C51</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Tripod</t>
+          <t>Vocal Microphone</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>1043.232336</v>
+        <v>912.8282939999998</v>
       </c>
       <c r="I29" t="n">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2309,13 +2307,13 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>53597.14</v>
+        <v>18687.28</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -2326,12 +2324,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>FBA79844</t>
+          <t>FBA79961</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>B0FN7DYB2M</t>
+          <t>B0G53H49BS</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2341,25 +2339,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>PB-08 (AM-C1 + AI-04)</t>
+          <t>AI-13</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Audio Mixer</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PB-08</t>
+          <t>4 channels Mixer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>3358.8228</v>
+        <v>1544.91011775</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>454</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -2371,16 +2369,16 @@
         <v>29</v>
       </c>
       <c r="M30" t="n">
-        <v>1</v>
+        <v>69</v>
       </c>
       <c r="N30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="P30" t="n">
-        <v>5033.59</v>
+        <v>962394.0600000001</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -2391,12 +2389,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>FBA79011</t>
+          <t>FBA79996</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>B0CH4RNWJX</t>
+          <t>B0GW8Z556N</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2406,25 +2404,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>AM-C43</t>
+          <t>AM-C49</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>XLR Microphone Kit - Boomarm</t>
+          <t>Vocal Microphone</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>1304.04042</v>
+        <v>534.6565721999999</v>
       </c>
       <c r="I31" t="n">
-        <v>143</v>
+        <v>10</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2436,16 +2434,16 @@
         <v>29</v>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N31" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>259528.14</v>
+        <v>8312.059999999999</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -2456,12 +2454,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>FBA76728</t>
+          <t>FBA76863</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>B0BLNCP74M</t>
+          <t>B0BPM2T7BQ</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2471,25 +2469,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>AM-C25</t>
+          <t>AI-03</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Boomarm</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>2157.615343358823</v>
+        <v>2179.9269789525</v>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2501,16 +2499,16 @@
         <v>29</v>
       </c>
       <c r="M32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P32" t="n">
-        <v>1626.51</v>
+        <v>152083.17</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -2521,12 +2519,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FBA79838</t>
+          <t>FBA79835</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>B0FQBX8J17</t>
+          <t>B0FJ8TWCQZ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2536,25 +2534,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>AH-40 SL</t>
+          <t>PB-06 (AA-05 + AM-C44 + AI-04)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>DJ Headphone</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>DJ Headphone</t>
+          <t>PB-06</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>477.9615959999999</v>
+        <v>4841.8232</v>
       </c>
       <c r="I33" t="n">
-        <v>184</v>
+        <v>16</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2569,13 +2567,13 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O33" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>169674.53</v>
+        <v>118574.49</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -2586,12 +2584,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>FBA79010</t>
+          <t>FBA79833</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>B0CH4T2BJD</t>
+          <t>B0FJ8PZ9H7</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2601,25 +2599,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>AM-C42</t>
+          <t>PB-04 (AI-04 Red + AM-C44 x 2)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Boomarm</t>
+          <t>PB-04</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>1499.646483</v>
+        <v>7169.514799999999</v>
       </c>
       <c r="I34" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2634,13 +2632,13 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O34" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="P34" t="n">
-        <v>43947.37</v>
+        <v>121653.73</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -2651,12 +2649,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>FBA79816</t>
+          <t>FBA79908</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>B0FPR962YS</t>
+          <t>B0FTVV1QJY</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2666,25 +2664,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>AM-W22</t>
+          <t>PB-14 (AM-C43+AH-40-SL+AI-12)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>PB-14</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>1679.60406096</v>
+        <v>2280.5034</v>
       </c>
       <c r="I35" t="n">
-        <v>173</v>
+        <v>4</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2696,16 +2694,16 @@
         <v>29</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N35" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P35" t="n">
-        <v>435345.64</v>
+        <v>16218.84</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -2716,12 +2714,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>FBA79109</t>
+          <t>FBA79822</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>B0CM9HYVDM</t>
+          <t>B0FJ2J6MTF</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2731,25 +2729,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>AM-W18</t>
+          <t>KB-01 (AM-W32 + AI-12)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Speaker Karaoke</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Microphone with Speaker</t>
+          <t>KB-01</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>612.8989974</v>
+        <v>2630.5268</v>
       </c>
       <c r="I36" t="n">
-        <v>235</v>
+        <v>25</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2761,16 +2759,16 @@
         <v>29</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N36" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="O36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>205107.74</v>
+        <v>99409.85000000001</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -2781,12 +2779,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>FBA80010</t>
+          <t>FBA79653</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>B0GW8ZQRFK</t>
+          <t>B0DN6LJZBR</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2796,7 +2794,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>AM-C52</t>
+          <t>AM-C45 Pro</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2806,15 +2804,15 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vocal Microphone</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>912.8282939999998</v>
+        <v>2458.088208</v>
       </c>
       <c r="I37" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2829,13 +2827,13 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P37" t="n">
-        <v>12458.18</v>
+        <v>33973.77</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -2846,12 +2844,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>FBK79010</t>
+          <t>FBA79355</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>B0FLYJFC22</t>
+          <t>B0D3M86SH1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2861,25 +2859,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>AM-C42</t>
+          <t>AA-19BL</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Boomarm</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>1499.646483</v>
+        <v>2973.2121576</v>
       </c>
       <c r="I38" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2891,16 +2889,16 @@
         <v>29</v>
       </c>
       <c r="M38" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P38" t="n">
-        <v>21418.21</v>
+        <v>87904.99000000001</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -2911,12 +2909,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>FBA79957</t>
+          <t>FBA76862</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>B0G3Q517Y2</t>
+          <t>B0BPLWW72Y</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2926,25 +2924,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>AM-W23</t>
+          <t>AM-C28</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Microphone Conference</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>Conference Microphone</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
-        <v>1566.15254442</v>
+        <v>874.2436631991176</v>
       </c>
       <c r="I39" t="n">
-        <v>51</v>
+        <v>177</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2959,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="O39" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="P39" t="n">
-        <v>120235.88</v>
+        <v>210581.01</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -2976,12 +2974,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>FBA79103</t>
+          <t>FBA80085</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>B0CM6NTWBP</t>
+          <t>B0GXPBHDRF</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2991,25 +2989,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>AI-10</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>Audio Mixer</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>06 channels Mixer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
-        <v>1499.646483</v>
+        <v>3998.590893</v>
       </c>
       <c r="I40" t="n">
-        <v>179</v>
+        <v>65</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -3021,16 +3019,16 @@
         <v>29</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="N40" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="P40" t="n">
-        <v>386100.53</v>
+        <v>351516.12</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -3041,12 +3039,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FBA79708</t>
+          <t>FBA80004</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>B0FFB6YJM1</t>
+          <t>B0GW92316G</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3056,25 +3054,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>SB-01</t>
+          <t>AM-W36 Pro</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sound Bar</t>
+          <t>Microphone Wireless Handheld</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sound Bar</t>
+          <t>Dual UHF Wireless Microphone With Receiver Box</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
-        <v>708</v>
+        <v>4694.545512</v>
       </c>
       <c r="I41" t="n">
-        <v>172</v>
+        <v>18</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -3086,16 +3084,16 @@
         <v>29</v>
       </c>
       <c r="M41" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>164979.95</v>
+        <v>106966.25</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -3106,12 +3104,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>FBA79835</t>
+          <t>FBA80003</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>B0FJ8TWCQZ</t>
+          <t>B0GW92TTMS</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3121,25 +3119,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>PB-06 (AA-05 + AM-C44 + AI-04)</t>
+          <t>AM-W32 Pro</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Wireless Handheld</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>PB-06</t>
+          <t>Dual UHF Wireless Microphone With Receiver</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
-        <v>4841.8232</v>
+        <v>3129.697008</v>
       </c>
       <c r="I42" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -3154,13 +3152,13 @@
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>118574.49</v>
+        <v>61869.39</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -3171,12 +3169,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FBA78974</t>
+          <t>FBA79356</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>B0CF5RRTDJ</t>
+          <t>B0D3Q2T5XX</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3186,7 +3184,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>AA-20</t>
+          <t>AA-19WL</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3201,10 +3199,10 @@
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>1107.780080664706</v>
+        <v>2973.2121576</v>
       </c>
       <c r="I43" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -3216,16 +3214,16 @@
         <v>29</v>
       </c>
       <c r="M43" t="n">
+        <v>4</v>
+      </c>
+      <c r="N43" t="n">
         <v>2</v>
-      </c>
-      <c r="N43" t="n">
-        <v>8</v>
       </c>
       <c r="O43" t="n">
         <v>2</v>
       </c>
       <c r="P43" t="n">
-        <v>24455.75</v>
+        <v>32233.45</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -3236,12 +3234,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FBA78973</t>
+          <t>FBA79845</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>B0CF5R3V95</t>
+          <t>B0FN7B3KWS</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3251,25 +3249,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>AA-19</t>
+          <t>UB-02 (AM-S1 + AA-21)</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>UB-02</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>1960.237563966397</v>
+        <v>5836.846399999999</v>
       </c>
       <c r="I44" t="n">
-        <v>121</v>
+        <v>27</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -3281,16 +3279,16 @@
         <v>29</v>
       </c>
       <c r="M44" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
         <v>3</v>
       </c>
-      <c r="O44" t="n">
-        <v>8</v>
-      </c>
       <c r="P44" t="n">
-        <v>317484.46</v>
+        <v>263232.76</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -3301,12 +3299,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>FBA78975</t>
+          <t>FBA79848</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>B0CF5TCQKL</t>
+          <t>B0GN97RFPR</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3316,25 +3314,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>AA-21</t>
+          <t>AM-S2</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Monitor Speakers Accessories</t>
+          <t>Monitor Speakers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Monitor Speaker Stand Pair</t>
+          <t>Studio Monitor Speaker</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>1722.835557825</v>
+        <v>3748.5845172</v>
       </c>
       <c r="I45" t="n">
-        <v>187</v>
+        <v>362</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -3346,16 +3344,16 @@
         <v>29</v>
       </c>
       <c r="M45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="P45" t="n">
-        <v>464511.44</v>
+        <v>1865928.8</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -3366,12 +3364,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FBK79009</t>
+          <t>FBA79106</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>B0FLYHJ6DK</t>
+          <t>B0CM9KJZWQ</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3381,25 +3379,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>AM-C41</t>
+          <t>AM-C44</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Tripod</t>
+          <t>Dynamic Microphone</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
-        <v>1043.232336</v>
+        <v>2738.484882</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -3411,16 +3409,16 @@
         <v>29</v>
       </c>
       <c r="M46" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>119737.23</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -3431,12 +3429,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FBA79964</t>
+          <t>FBA79108</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>B0G53KWRWH</t>
+          <t>B0CM9L1QZG</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3446,25 +3444,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>AM-Pro12</t>
+          <t>AM-W16</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Audio Mixer</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>12 channels Mixer</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
-        <v>13162.63420323</v>
+        <v>756.3434436</v>
       </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -3479,13 +3477,13 @@
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P47" t="n">
-        <v>34958.98</v>
+        <v>45965.17</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -3496,12 +3494,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FBA76863</t>
+          <t>FBA79446</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>B0BPM2T7BQ</t>
+          <t>B0DFMMTWLY</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3511,25 +3509,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>AI-03</t>
+          <t>AM-W33</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>Microphone Wireless Handheld</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>Wireless Microphone</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>2179.9269789525</v>
+        <v>1194.50102472</v>
       </c>
       <c r="I48" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -3544,13 +3542,13 @@
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="O48" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P48" t="n">
-        <v>152083.17</v>
+        <v>53069.79</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -3561,12 +3559,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>FBA79969</t>
+          <t>FBA79379</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>B0G3B677Z5</t>
+          <t>B0D3LZWTHV</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3576,25 +3574,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>UB-03 (AM-S1 + AA-22)</t>
+          <t>AM-C45</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>UB-03</t>
+          <t>Dynamic Microphone</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
-        <v>5619.632</v>
+        <v>2021.262651</v>
       </c>
       <c r="I49" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -3606,16 +3604,16 @@
         <v>29</v>
       </c>
       <c r="M49" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P49" t="n">
-        <v>163601.96</v>
+        <v>74497.81</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -3626,12 +3624,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>FBA78203</t>
+          <t>FBA80010</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>B0C4YTNJG7</t>
+          <t>B0GW8ZQRFK</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3641,25 +3639,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>AM-C30</t>
+          <t>AM-C52</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>RGB USB Microphone Kit - Tripod</t>
+          <t>Vocal Microphone</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>3196.1775</v>
+        <v>912.8282939999998</v>
       </c>
       <c r="I50" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -3674,13 +3672,13 @@
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>3165.42</v>
+        <v>12458.18</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -3691,12 +3689,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FBA79465</t>
+          <t>FBA79832</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>B0DFMQCGT1</t>
+          <t>B0FJ8S53GW</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3706,25 +3704,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>AM-W21</t>
+          <t>GB-05 (AM-C43 + AI-06)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>GB-05</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
-        <v>2803.686903</v>
+        <v>3909.104</v>
       </c>
       <c r="I51" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -3736,16 +3734,16 @@
         <v>29</v>
       </c>
       <c r="M51" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P51" t="n">
-        <v>34447.2</v>
+        <v>83681.85000000001</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -3756,12 +3754,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>FBA79830</t>
+          <t>FBA79825</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>B0FJ8TSQK1</t>
+          <t>B0FJ2DT13L</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3771,7 +3769,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>GB-03 (AI-12 + AM-C43)</t>
+          <t>GB-02 (AM-C43 + AI-11)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3781,12 +3779,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>GB-03</t>
+          <t>GB-02</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
-        <v>1828.2802</v>
+        <v>1983.58</v>
       </c>
       <c r="I52" t="n">
         <v>21</v>
@@ -3801,16 +3799,16 @@
         <v>29</v>
       </c>
       <c r="M52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O52" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>61655.41</v>
+        <v>63123.84</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -3821,12 +3819,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FBA80004</t>
+          <t>FBA75676</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>B0GW92316G</t>
+          <t>B0B4DS678Q</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3836,25 +3834,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>AM-W36 Pro</t>
+          <t>AM-C4</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Microphone Wireless Handheld</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dual UHF Wireless Microphone With Receiver Box</t>
+          <t>USB Microphone Kit - Tripod</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
-        <v>4694.545512</v>
+        <v>1700.734990628047</v>
       </c>
       <c r="I53" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -3866,16 +3864,16 @@
         <v>29</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P53" t="n">
-        <v>106966.25</v>
+        <v>14089.43</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -3886,12 +3884,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FBA79959</t>
+          <t>FBA78975</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>B0G39ZHDYP</t>
+          <t>B0CF5TCQKL</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3901,25 +3899,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>AM-W47 Wired</t>
+          <t>AA-21</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Voice Amplifier</t>
+          <t>Monitor Speakers Accessories</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Wired Voice Amplifier</t>
+          <t>Monitor Speaker Stand Pair</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
-        <v>503.35960212</v>
+        <v>1722.835557825</v>
       </c>
       <c r="I54" t="n">
-        <v>120</v>
+        <v>187</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -3931,16 +3929,16 @@
         <v>29</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N54" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O54" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="P54" t="n">
-        <v>115102.29</v>
+        <v>464511.44</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -3951,12 +3949,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FBA79827</t>
+          <t>FBA79981</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>B0FJ8S5XJ8</t>
+          <t>B0GN8MFDGZ</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3966,25 +3964,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>PB-03 (AI-04 Red + AM-C11 x 2)</t>
+          <t>AK-61 Neo</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Electric Keyboard</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>PB-03</t>
+          <t>61 Key Electronic Keyboard With LED DIsplay</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
-        <v>7722.439199999999</v>
+        <v>2870.1202068</v>
       </c>
       <c r="I55" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -3999,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P55" t="n">
-        <v>155003.82</v>
+        <v>45439.37</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -4016,12 +4014,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>FBA79907</t>
+          <t>FBA79995</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>B0FTVS34SD</t>
+          <t>B0GW8VBCBL</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4031,25 +4029,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>PB-13 (AM-C43+AH-40-SL+AI-11)</t>
+          <t>AM-C50</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>PB-13</t>
+          <t>Vocal Microphone</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
-        <v>2436.8652</v>
+        <v>534.6565721999999</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -4069,7 +4067,9 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="P56" t="inlineStr"/>
+      <c r="P56" t="n">
+        <v>18286.52</v>
+      </c>
       <c r="Q56" t="inlineStr">
         <is>
           <t>2026-07-18</t>
@@ -4079,12 +4079,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FBA75689</t>
+          <t>FBA79982</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>B0B4G59Y8W</t>
+          <t>B0GN8MPYPG</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4094,25 +4094,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>AM-W13</t>
+          <t>AK-61 Pro</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Microphone Wireless Handheld</t>
+          <t>Electric Keyboard</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Wireless Microphone</t>
+          <t>61 Key Electronic Keyboard With LCD DIsplay</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
-        <v>1305.459898830882</v>
+        <v>3317.4116676</v>
       </c>
       <c r="I57" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -4124,16 +4124,16 @@
         <v>29</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="P57" t="n">
-        <v>32691.99</v>
+        <v>26914.61</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -4144,12 +4144,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FBA79848</t>
+          <t>FBA80084</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>B0GN97RFPR</t>
+          <t>B0GXP97CZG</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4159,25 +4159,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>AM-S2</t>
+          <t>BE-4</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Monitor Speakers</t>
+          <t>Audio Mixer</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Studio Monitor Speaker</t>
+          <t>04 channels Mixer</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>3748.5845172</v>
+        <v>1948.404289679999</v>
       </c>
       <c r="I58" t="n">
-        <v>362</v>
+        <v>7</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -4195,10 +4195,10 @@
         <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="P58" t="n">
-        <v>1865928.8</v>
+        <v>22020.17</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -4209,12 +4209,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FBA79106</t>
+          <t>FBA79783</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>B0CM9KJZWQ</t>
+          <t>B0FF9R3GKK</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4224,25 +4224,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>AM-C44</t>
+          <t>AM-C47</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dynamic Microphone</t>
+          <t>USB Microphone Kit - Boomarm</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
-        <v>2738.484882</v>
+        <v>1693.3496544</v>
       </c>
       <c r="I59" t="n">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -4257,13 +4257,13 @@
         <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O59" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P59" t="n">
-        <v>119737.23</v>
+        <v>151352.91</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -4274,12 +4274,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FBA78961</t>
+          <t>FBA78424</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>B0CBCB9S14</t>
+          <t>B0C55MY66L</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4289,25 +4289,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>AM-C40</t>
+          <t>AM-C37</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Condenser Mic with Boom Arm</t>
+          <t>USB/XLR Dynamic Mic</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>3103.426797881559</v>
       </c>
       <c r="I60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -4322,13 +4322,13 @@
         <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>1</v>
       </c>
       <c r="P60" t="n">
-        <v>4243.48</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -4339,12 +4339,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FBA79694</t>
+          <t>FBA76597</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>B0DT6T6N6B</t>
+          <t>B0BQ7H7418</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>AA-26</t>
+          <t>AA-06</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4369,10 +4369,10 @@
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
-        <v>260.808084</v>
+        <v>598.3056269558823</v>
       </c>
       <c r="I61" t="n">
-        <v>381</v>
+        <v>69</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -4384,16 +4384,16 @@
         <v>29</v>
       </c>
       <c r="M61" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O61" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="P61" t="n">
-        <v>157302.05</v>
+        <v>64429.7</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -4404,12 +4404,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FBA79996</t>
+          <t>FBA79967</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>B0GW8Z556N</t>
+          <t>B0G2C2RCXN</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4419,25 +4419,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>AM-C49</t>
+          <t>AM-W19</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vocal Microphone</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
-        <v>534.6565721999999</v>
+        <v>1159.29193338</v>
       </c>
       <c r="I62" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         <v>29</v>
       </c>
       <c r="M62" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="N62" t="n">
         <v>0</v>
@@ -4457,9 +4457,7 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
-      <c r="P62" t="n">
-        <v>8312.059999999999</v>
-      </c>
+      <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr">
         <is>
           <t>2026-07-18</t>
@@ -4469,12 +4467,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FBA79108</t>
+          <t>FBA78960</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>B0CM9L1QZG</t>
+          <t>B0CBCB82MT</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4484,25 +4482,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>AM-W16</t>
+          <t>AM-C39</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>XLR Microphone Kit - Tripod</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
-        <v>756.3434436</v>
+        <v>734.122339149</v>
       </c>
       <c r="I63" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -4517,13 +4515,13 @@
         <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="O63" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="P63" t="n">
-        <v>45965.17</v>
+        <v>68573.92</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -4534,12 +4532,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>FBA75686</t>
+          <t>FBA78925</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>B0B4G89VQJ</t>
+          <t>B0CBC7QMNV</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4549,25 +4547,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>AM-W10</t>
+          <t>AM-C11X</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Wireless Microphone</t>
+          <t>XLR Dynamic Mic</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
-        <v>4934.296426588235</v>
+        <v>2173.4007</v>
       </c>
       <c r="I64" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -4579,16 +4577,16 @@
         <v>29</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N64" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>21111.87</v>
+        <v>51861.01</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -4599,12 +4597,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FBA75676</t>
+          <t>FBA79905</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>B0B4DS678Q</t>
+          <t>B0FTVSH458</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4614,25 +4612,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>AM-C4</t>
+          <t>PB-11 (AM-C44+AA-05+AH-45-BK)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Tripod</t>
+          <t>PB-11</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
-        <v>1700.734990628047</v>
+        <v>3425.8468</v>
       </c>
       <c r="I65" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -4644,16 +4642,16 @@
         <v>29</v>
       </c>
       <c r="M65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O65" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>14089.43</v>
+        <v>25797.25</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -4664,12 +4662,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>FBA79836</t>
+          <t>FBA79972</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>B0FJ8Z1W81</t>
+          <t>B0GCP1J2HC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4679,25 +4677,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>PB-07 (AA-05 + AM-C45 + AI-04)</t>
+          <t>M8</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Audio Mixer</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>PB-07</t>
+          <t>8 channels Mixer</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
-        <v>4180.2798</v>
+        <v>4119.760313999999</v>
       </c>
       <c r="I66" t="n">
-        <v>14</v>
+        <v>136</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -4712,13 +4710,13 @@
         <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P66" t="n">
-        <v>81238.77</v>
+        <v>828116.3199999999</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -4729,12 +4727,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>FBA79958</t>
+          <t>FBA79838</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>B0G3Q59X8C</t>
+          <t>B0FQBX8J17</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4744,25 +4742,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>AM-W24</t>
+          <t>AH-40 SL</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>DJ Headphone</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>DJ Headphone</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
-        <v>905.00405148</v>
+        <v>477.9615959999999</v>
       </c>
       <c r="I67" t="n">
-        <v>48</v>
+        <v>184</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -4777,13 +4775,13 @@
         <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="P67" t="n">
-        <v>64650.55</v>
+        <v>169674.53</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -4794,12 +4792,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>FBA79821</t>
+          <t>FBK79010</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>B0FJ2JJZL3</t>
+          <t>B0FLYJFC22</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4809,25 +4807,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>UB-01 (AI-04, AM-S1, AA-21, AM-C2)</t>
+          <t>AM-C42</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>UB-01</t>
+          <t>USB Microphone Kit - Boomarm</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
-        <v>9527.5088</v>
+        <v>1499.646483</v>
       </c>
       <c r="I68" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -4839,16 +4837,16 @@
         <v>29</v>
       </c>
       <c r="M68" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="N68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>1</v>
       </c>
       <c r="P68" t="n">
-        <v>357978.96</v>
+        <v>21418.21</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -4859,12 +4857,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>FBA79016</t>
+          <t>FBA79963</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>B0CH4R1V6S</t>
+          <t>B0G53CB72D</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4874,25 +4872,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>AM-C3a</t>
+          <t>AM-Pro8</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Audio Mixer</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vocal Microphone</t>
+          <t>8 channels Mixer</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>521.6161679999999</v>
+        <v>12112.09532316</v>
       </c>
       <c r="I69" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -4907,13 +4905,13 @@
         <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="O69" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>19005.74</v>
+        <v>47194.42</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -4924,12 +4922,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>FBA79722</t>
+          <t>FBA79966</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>B0F2HYY7JF</t>
+          <t>B0G53KWRVW</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4939,25 +4937,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>AM-W21</t>
+          <t>AM-Mix10</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Audio Mixer</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>10 channels mixer</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
-        <v>2803.686903</v>
+        <v>5808.86204274</v>
       </c>
       <c r="I70" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -4969,16 +4967,16 @@
         <v>29</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="N70" t="n">
         <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P70" t="n">
-        <v>14763.09</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -4989,12 +4987,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>FBA79064</t>
+          <t>FBA75673</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>B0CJR76Y7G</t>
+          <t>B0B4DPX2J2</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5004,25 +5002,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>AA-25</t>
+          <t>AM-C1</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>USB Microphone Kit - Boomarm</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
-        <v>326.010105</v>
+        <v>1475.964687829412</v>
       </c>
       <c r="I71" t="n">
-        <v>33</v>
+        <v>2480</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -5034,16 +5032,16 @@
         <v>29</v>
       </c>
       <c r="M71" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="N71" t="n">
-        <v>5</v>
+        <v>205</v>
       </c>
       <c r="O71" t="n">
-        <v>7</v>
+        <v>197</v>
       </c>
       <c r="P71" t="n">
-        <v>18819.55</v>
+        <v>4726055.07</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -5054,12 +5052,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>FBA79783</t>
+          <t>FBA75686</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>B0FF9R3GKK</t>
+          <t>B0B4G89VQJ</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5069,25 +5067,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>AM-C47</t>
+          <t>AM-W10</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Boomarm</t>
+          <t>Wireless Microphone</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
-        <v>1693.3496544</v>
+        <v>4934.296426588235</v>
       </c>
       <c r="I72" t="n">
-        <v>68</v>
+        <v>6</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -5102,13 +5100,13 @@
         <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O72" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P72" t="n">
-        <v>151352.91</v>
+        <v>21111.87</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -5119,12 +5117,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>FBA79379</t>
+          <t>FBA79011</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>B0D3LZWTHV</t>
+          <t>B0CH4RNWJX</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5134,25 +5132,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>AM-C45</t>
+          <t>AM-C43</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dynamic Microphone</t>
+          <t>XLR Microphone Kit - Boomarm</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
-        <v>2021.262651</v>
+        <v>1304.04042</v>
       </c>
       <c r="I73" t="n">
-        <v>29</v>
+        <v>143</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -5167,13 +5165,13 @@
         <v>1</v>
       </c>
       <c r="N73" t="n">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="O73" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="P73" t="n">
-        <v>74497.81</v>
+        <v>259528.14</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -5184,12 +5182,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>FBA79825</t>
+          <t>FBA79831</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>B0FJ2DT13L</t>
+          <t>B0FJ8W5Y9Q</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5199,7 +5197,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>GB-02 (AM-C43 + AI-11)</t>
+          <t>GB-04 (AM-C45 + AI-06)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -5209,15 +5207,15 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>GB-02</t>
+          <t>GB-04</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
-        <v>1983.58</v>
+        <v>4630.8156</v>
       </c>
       <c r="I74" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -5232,13 +5230,13 @@
         <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>63123.84</v>
+        <v>47190.19</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -5249,12 +5247,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>FBA78960</t>
+          <t>FBA76722</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>B0CBCB82MT</t>
+          <t>B0BLKDC4PP</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5264,7 +5262,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>AM-C39</t>
+          <t>AM-C19</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5274,15 +5272,15 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>XLR Microphone Kit - Tripod</t>
+          <t>USB Microphone Kit - Tripod</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
-        <v>734.122339149</v>
+        <v>1642.572937873306</v>
       </c>
       <c r="I75" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -5297,14 +5295,12 @@
         <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>11</v>
-      </c>
-      <c r="P75" t="n">
-        <v>68573.92</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr">
         <is>
           <t>2026-07-18</t>
@@ -5314,12 +5310,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>FBA75677</t>
+          <t>FBA79230</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>B0B4KC7VBM</t>
+          <t>B0CX1XK5R6</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5329,25 +5325,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>AM-C5</t>
+          <t>AM-W46</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Microphone Conference</t>
+          <t>Speaker Karaoke</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Conference Microphone</t>
+          <t>Microphone with Speaker</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
-        <v>1291.959696295941</v>
+        <v>4277.252577599999</v>
       </c>
       <c r="I76" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -5362,13 +5358,13 @@
         <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O76" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>136640.87</v>
+        <v>18315.74</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -5379,12 +5375,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>FBA80005</t>
+          <t>FBA79959</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>B0GW96CQMG</t>
+          <t>B0G39ZHDYP</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5394,25 +5390,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>T-835</t>
+          <t>AM-W47 Wired</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Microphone Wireless Handheld</t>
+          <t>Voice Amplifier</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Quad UHF Wireless Microphone With Receiver Box</t>
+          <t>Wired Voice Amplifier</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
-        <v>6259.394015999999</v>
+        <v>503.35960212</v>
       </c>
       <c r="I77" t="n">
-        <v>18</v>
+        <v>120</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -5427,13 +5423,13 @@
         <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P77" t="n">
-        <v>142206.19</v>
+        <v>115102.29</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -5444,12 +5440,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>FBA79839</t>
+          <t>FBA80007</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>B0FQBXS6Y2</t>
+          <t>B0GN2LHJY4</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5459,25 +5455,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>AH-45 BK</t>
+          <t>MT-12</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>DJ Headphone</t>
+          <t>Audio Mixer</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>DJ Headphone</t>
+          <t>12 channels Mixer</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
-        <v>614.5220519999999</v>
+        <v>4119.760313999999</v>
       </c>
       <c r="I78" t="n">
-        <v>217</v>
+        <v>11</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -5489,16 +5485,16 @@
         <v>29</v>
       </c>
       <c r="M78" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O78" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="P78" t="n">
-        <v>240999.64</v>
+        <v>74737.64999999999</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -5509,12 +5505,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>FBA79842</t>
+          <t>FBA78974</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>B0G4DNF8RZ</t>
+          <t>B0CF5RRTDJ</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5524,25 +5520,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>AM-C48</t>
+          <t>AA-20</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
-        <v>1956.06063</v>
+        <v>1107.780080664706</v>
       </c>
       <c r="I79" t="n">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -5554,16 +5550,16 @@
         <v>29</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O79" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P79" t="n">
-        <v>142250.59</v>
+        <v>24455.75</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -5574,12 +5570,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>FBA75690</t>
+          <t>FBA78204</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>B0B4K87PR4</t>
+          <t>B0C4YT43Z3</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5589,25 +5585,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>AM-C10</t>
+          <t>AM-C31</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Microphone Conference</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Conference Microphone</t>
+          <t>USB Microphone Kit - Tripod</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
-        <v>2311.522194589411</v>
+        <v>3835.413</v>
       </c>
       <c r="I80" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -5619,17 +5615,15 @@
         <v>29</v>
       </c>
       <c r="M80" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
       </c>
-      <c r="P80" t="n">
-        <v>81298.17999999999</v>
-      </c>
+      <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr">
         <is>
           <t>2026-07-18</t>
@@ -5639,12 +5633,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>FBA75681</t>
+          <t>FBA75679</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>B0B4FZS38V</t>
+          <t>B0B4JRQP22</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5654,25 +5648,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>AM-C7</t>
+          <t>AA-02</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Boomarm</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
-        <v>2051.276637829411</v>
+        <v>1330.281037275</v>
       </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>153</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -5684,16 +5678,16 @@
         <v>29</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P81" t="n">
-        <v>2050.99</v>
+        <v>259341.18</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -5704,12 +5698,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>FBA79482</t>
+          <t>FBA79844</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>B0DXFPM4N2</t>
+          <t>B0FN7DYB2M</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5719,25 +5713,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>AM-S1</t>
+          <t>PB-08 (AM-C1 + AI-04)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Monitor Speakers</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Studio Monitor Speaker</t>
+          <t>PB-08</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
-        <v>4486.010979600001</v>
+        <v>3358.8228</v>
       </c>
       <c r="I82" t="n">
-        <v>128</v>
+        <v>1</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -5749,16 +5743,16 @@
         <v>29</v>
       </c>
       <c r="M82" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="N82" t="n">
         <v>1</v>
       </c>
       <c r="O82" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="P82" t="n">
-        <v>843154.5699999999</v>
+        <v>5033.59</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -5769,12 +5763,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>FBA79444</t>
+          <t>FBA80002</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>B0DFMLQBMC</t>
+          <t>B0GW96SHSK</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5784,25 +5778,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>AM-W20</t>
+          <t>AM-W33 Pro</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Microphone Wireless Handheld</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>Single UHF Wireless Microphone With Receiver</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
-        <v>2164.7070972</v>
+        <v>1825.656588</v>
       </c>
       <c r="I83" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -5817,13 +5811,13 @@
         <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>12578.82</v>
+        <v>30197.39</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
@@ -5834,12 +5828,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>FBA79909</t>
+          <t>FBA76728</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>B0FVM17Q4W</t>
+          <t>B0BLNCP74M</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5849,25 +5843,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>AM-W20</t>
+          <t>AM-C25</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>USB Microphone Kit - Boomarm</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
-        <v>2164.7070972</v>
+        <v>2157.615343358823</v>
       </c>
       <c r="I84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -5879,7 +5873,7 @@
         <v>29</v>
       </c>
       <c r="M84" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="N84" t="n">
         <v>0</v>
@@ -5887,7 +5881,9 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
-      <c r="P84" t="inlineStr"/>
+      <c r="P84" t="n">
+        <v>1626.51</v>
+      </c>
       <c r="Q84" t="inlineStr">
         <is>
           <t>2026-07-18</t>
@@ -5897,12 +5893,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>FBA79979</t>
+          <t>FBA75681</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>B0GN8RQJRG</t>
+          <t>B0B4FZS38V</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5912,25 +5908,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>AK-37-B</t>
+          <t>AM-C7</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Electric Keyboard</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>37 Key Electronic Keyboard Black</t>
+          <t>USB Microphone Kit - Boomarm</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
-        <v>2261.3068296</v>
+        <v>2051.276637829411</v>
       </c>
       <c r="I85" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -5945,13 +5941,13 @@
         <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O85" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>61514.88</v>
+        <v>2050.99</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -5962,12 +5958,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>FBA80016</t>
+          <t>FBA79821</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>B0GKPXQ8G3</t>
+          <t>B0FJ2JJZL3</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5977,25 +5973,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>AM-W22</t>
+          <t>UB-01 (AI-04, AM-S1, AA-21, AM-C2)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>UB-01</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
-        <v>1679.6</v>
+        <v>9527.5088</v>
       </c>
       <c r="I86" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -6007,16 +6003,16 @@
         <v>29</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N86" t="n">
         <v>2</v>
       </c>
       <c r="O86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P86" t="n">
-        <v>84370.52</v>
+        <v>357978.96</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -6027,12 +6023,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>FBA78206</t>
+          <t>FBA75678</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>B0C4YSV3XL</t>
+          <t>B0B4G8PH2P</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6042,25 +6038,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>AM-W15</t>
+          <t>AA-01</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Wireless Mic with Charging Case</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
-        <v>11761.9332</v>
+        <v>1224.499030661912</v>
       </c>
       <c r="I87" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -6075,13 +6071,13 @@
         <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O87" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P87" t="n">
-        <v>16505.6</v>
+        <v>48433.97</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -6092,12 +6088,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>FBA79845</t>
+          <t>FBA76414</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>B0FN7B3KWS</t>
+          <t>B0BLJVJ2GN</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6107,25 +6103,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>UB-02 (AM-S1 + AA-21)</t>
+          <t>AA-05</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>UB-02</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
-        <v>5836.846399999999</v>
+        <v>280.0829144294117</v>
       </c>
       <c r="I88" t="n">
-        <v>27</v>
+        <v>589</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -6137,16 +6133,16 @@
         <v>29</v>
       </c>
       <c r="M88" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="O88" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="P88" t="n">
-        <v>263232.76</v>
+        <v>274807.88</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -6157,12 +6153,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>FBA80084</t>
+          <t>FBA79969</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>B0GXP97CZG</t>
+          <t>B0G3B677Z5</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6172,25 +6168,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>BE-4</t>
+          <t>UB-03 (AM-S1 + AA-22)</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Audio Mixer</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>04 channels Mixer</t>
+          <t>UB-03</t>
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
-        <v>1948.404289679999</v>
+        <v>5619.632</v>
       </c>
       <c r="I89" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -6202,16 +6198,16 @@
         <v>29</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N89" t="n">
         <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>22020.17</v>
+        <v>163601.96</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -6222,12 +6218,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>FBA79834</t>
+          <t>FBA78203</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>B0FJ8T4WXM</t>
+          <t>B0C4YTNJG7</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6237,25 +6233,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>PB-05 (AA-05 + AM-C11 + AI-04)</t>
+          <t>AM-C30</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>PB-05</t>
+          <t>RGB USB Microphone Kit - Tripod</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
-        <v>5118.2854</v>
+        <v>3196.1775</v>
       </c>
       <c r="I90" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -6270,13 +6266,13 @@
         <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O90" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P90" t="n">
-        <v>73409.8</v>
+        <v>3165.42</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -6287,12 +6283,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>FBA79824</t>
+          <t>FBA79823</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>B0FJ2K95XT</t>
+          <t>B0FJ2HZCVN</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6302,7 +6298,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>GB-01 (AM-C43 +AI-10)</t>
+          <t>PB-01 (AM-C11 + AI-04)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -6312,15 +6308,15 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>GB-01</t>
+          <t>PB-01</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
-        <v>2585.9936</v>
+        <v>4859.948</v>
       </c>
       <c r="I91" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -6335,13 +6331,13 @@
         <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="O91" t="n">
         <v>1</v>
       </c>
       <c r="P91" t="n">
-        <v>46140.06</v>
+        <v>82498.16</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -6352,12 +6348,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>FBA79841</t>
+          <t>FBA79906</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>B0FQBTRM28</t>
+          <t>B0FTVVLNS9</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6367,25 +6363,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>AH-60-BL</t>
+          <t>PB-12 (AM-C11+AA-05+AI-04+AH-60-RD)</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Headphone</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Headphone</t>
+          <t>PB-12</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
-        <v>1092.483648</v>
+        <v>6152.0362</v>
       </c>
       <c r="I92" t="n">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -6397,16 +6393,16 @@
         <v>29</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N92" t="n">
         <v>1</v>
       </c>
       <c r="O92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>83647.21000000001</v>
+        <v>211423.58</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -6417,12 +6413,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>FBA79355</t>
+          <t>FBA79964</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>B0D3M86SH1</t>
+          <t>B0G53KWRWH</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6432,25 +6428,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>AA-19BL</t>
+          <t>AM-Pro12</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Audio Mixer</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>12 channels Mixer</t>
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
-        <v>2973.2121576</v>
+        <v>13162.63420323</v>
       </c>
       <c r="I93" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -6462,16 +6458,16 @@
         <v>29</v>
       </c>
       <c r="M93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P93" t="n">
-        <v>87904.99000000001</v>
+        <v>34958.98</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -6482,12 +6478,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>FBA80002</t>
+          <t>FBA79444</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>B0GW96SHSK</t>
+          <t>B0DFMLQBMC</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6497,25 +6493,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>AM-W33 Pro</t>
+          <t>AM-W20</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Microphone Wireless Handheld</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Single UHF Wireless Microphone With Receiver</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
-        <v>1825.656588</v>
+        <v>2164.7070972</v>
       </c>
       <c r="I94" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -6530,13 +6526,13 @@
         <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O94" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P94" t="n">
-        <v>30197.39</v>
+        <v>12578.82</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -6547,12 +6543,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>FBA79972</t>
+          <t>FBK79009</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>B0GCP1J2HC</t>
+          <t>B0FLYHJ6DK</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6562,25 +6558,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>AM-C41</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Audio Mixer</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>8 channels Mixer</t>
+          <t>USB Microphone Kit - Tripod</t>
         </is>
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
-        <v>4119.760313999999</v>
+        <v>1043.232336</v>
       </c>
       <c r="I95" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -6592,16 +6588,16 @@
         <v>29</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N95" t="n">
         <v>0</v>
       </c>
       <c r="O95" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="P95" t="n">
-        <v>828116.3199999999</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -6612,12 +6608,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>FBA79995</t>
+          <t>FBA79846</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>B0GW8VBCBL</t>
+          <t>B0FN7C25VS</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6627,7 +6623,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>AM-C50</t>
+          <t>AM-C11X Pro</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6637,15 +6633,15 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vocal Microphone</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
-        <v>534.6565721999999</v>
+        <v>2263.0394</v>
       </c>
       <c r="I96" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -6660,13 +6656,13 @@
         <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>18286.52</v>
+        <v>36141.32</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -6677,12 +6673,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>FBA75675</t>
+          <t>FBA79830</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>B0B4G8ZB64</t>
+          <t>B0FJ8TSQK1</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6692,25 +6688,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>AM-C3</t>
+          <t>GB-03 (AI-12 + AM-C43)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vocal Microphone</t>
+          <t>GB-03</t>
         </is>
       </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
-        <v>659.7098370441175</v>
+        <v>1828.2802</v>
       </c>
       <c r="I97" t="n">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -6722,16 +6718,16 @@
         <v>29</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N97" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="P97" t="n">
-        <v>51349.02</v>
+        <v>61655.41</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -6742,12 +6738,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>FBA76597</t>
+          <t>FBA79465</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>B0BQ7H7418</t>
+          <t>B0DFMQCGT1</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6757,25 +6753,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>AA-06</t>
+          <t>AM-W21</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
-        <v>598.3056269558823</v>
+        <v>2803.686903</v>
       </c>
       <c r="I98" t="n">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -6787,16 +6783,16 @@
         <v>29</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>64429.7</v>
+        <v>34447.2</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -6807,12 +6803,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>FBA79831</t>
+          <t>FBA75691</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>B0FJ8W5Y9Q</t>
+          <t>B0B4G5JG4P</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6822,25 +6818,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>GB-04 (AM-C45 + AI-06)</t>
+          <t>AM-W14</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Wireless Handheld</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>GB-04</t>
+          <t>Wireless Microphone</t>
         </is>
       </c>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
-        <v>4630.8156</v>
+        <v>3221.74692</v>
       </c>
       <c r="I99" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -6852,16 +6848,16 @@
         <v>29</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N99" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P99" t="n">
-        <v>47190.19</v>
+        <v>74664.16</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -6872,12 +6868,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>FBA77171</t>
+          <t>FBA79010</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>B0CH4VCD6R</t>
+          <t>B0CH4T2BJD</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6887,25 +6883,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>AC-6XL</t>
+          <t>AM-C42</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>USB Microphone Kit - Boomarm</t>
         </is>
       </c>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
-        <v>169.5252546</v>
+        <v>1499.646483</v>
       </c>
       <c r="I100" t="n">
-        <v>179</v>
+        <v>25</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -6917,16 +6913,16 @@
         <v>29</v>
       </c>
       <c r="M100" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O100" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P100" t="n">
-        <v>73713.02</v>
+        <v>43947.37</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -6937,12 +6933,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>FBA75691</t>
+          <t>FBA79016</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>B0B4G5JG4P</t>
+          <t>B0CH4R1V6S</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6952,25 +6948,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>AM-W14</t>
+          <t>AM-C3a</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Microphone Wireless Handheld</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Wireless Microphone</t>
+          <t>Vocal Microphone</t>
         </is>
       </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
-        <v>3221.74692</v>
+        <v>521.6161679999999</v>
       </c>
       <c r="I101" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -6982,16 +6978,16 @@
         <v>29</v>
       </c>
       <c r="M101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="O101" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P101" t="n">
-        <v>74664.16</v>
+        <v>19005.74</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -7002,12 +6998,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>FBA79653</t>
+          <t>FBA75692</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>B0DN6LJZBR</t>
+          <t>B0B4G1HPL5</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -7017,7 +7013,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>AM-C45 Pro</t>
+          <t>AM-C11</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -7027,15 +7023,15 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>USB/XLR Dynamic Mic</t>
         </is>
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
-        <v>2458.088208</v>
+        <v>2975.579697881559</v>
       </c>
       <c r="I102" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -7050,13 +7046,13 @@
         <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="O102" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="P102" t="n">
-        <v>33973.77</v>
+        <v>89131.53999999999</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -7067,12 +7063,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>FBA79815</t>
+          <t>FBA79105</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>B0FPR7VFCH</t>
+          <t>B0CM6WH4ZT</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -7082,25 +7078,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>AM-W19</t>
+          <t>AI-12</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
-        <v>1159.29193338</v>
+        <v>678.1010183999999</v>
       </c>
       <c r="I103" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -7112,16 +7108,16 @@
         <v>29</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N103" t="n">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="O103" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P103" t="n">
-        <v>74082.34</v>
+        <v>94324.98</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -7132,12 +7128,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>FBA79960</t>
+          <t>FBA79103</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>B0G3B152FR</t>
+          <t>B0CM6NTWBP</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -7147,25 +7143,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>AM-W47 Wireless</t>
+          <t>AI-10</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Voice Amplifier</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Wireless Voice Amplifier</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
-        <v>920.65253652</v>
+        <v>1499.646483</v>
       </c>
       <c r="I104" t="n">
-        <v>51</v>
+        <v>179</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -7177,16 +7173,16 @@
         <v>29</v>
       </c>
       <c r="M104" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>13</v>
+        <v>128</v>
       </c>
       <c r="O104" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="P104" t="n">
-        <v>77922.14</v>
+        <v>386100.53</v>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
@@ -7197,12 +7193,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>FBA79968</t>
+          <t>FBA79847</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>B0G53M9258</t>
+          <t>B0FN7FYZM3</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -7212,25 +7208,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>AI-14</t>
+          <t>PB-09 (AM-C45 + AI-06 + AA-05)</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Audio Mixer</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>8 channels Mixer</t>
+          <t>PB-09</t>
         </is>
       </c>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
-        <v>3065.101673616</v>
+        <v>4889.153</v>
       </c>
       <c r="I105" t="n">
-        <v>93</v>
+        <v>8</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -7245,13 +7241,13 @@
         <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O105" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P105" t="n">
-        <v>465048.08</v>
+        <v>39150.73</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -7262,12 +7258,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>FBA79005</t>
+          <t>FBA75680</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>B0CKHVHVQ1</t>
+          <t>B0B4G1PXWV</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -7277,25 +7273,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>AM-W45</t>
+          <t>AM-C6</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Microphone Conference</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Wireless Conference Microphone</t>
+          <t>USB Microphone Kit - Tripod</t>
         </is>
       </c>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
-        <v>2738.484882</v>
+        <v>1815.59502123</v>
       </c>
       <c r="I106" t="n">
-        <v>574</v>
+        <v>9</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -7310,13 +7306,13 @@
         <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O106" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="P106" t="n">
-        <v>2197559.03</v>
+        <v>12598.26</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -7327,12 +7323,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>FBA79654</t>
+          <t>FBA75675</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>B0DN6MNS1X</t>
+          <t>B0B4G8ZB64</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -7342,7 +7338,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>AM-C11 Pro</t>
+          <t>AM-C3</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -7352,15 +7348,15 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Vocal Microphone</t>
         </is>
       </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
-        <v>3140.890488</v>
+        <v>659.7098370441175</v>
       </c>
       <c r="I107" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
@@ -7375,13 +7371,13 @@
         <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>74</v>
+        <v>6</v>
       </c>
       <c r="O107" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="P107" t="n">
-        <v>279351.35</v>
+        <v>51349.02</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -7392,12 +7388,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>FBA79820</t>
+          <t>FBA78206</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>B0FQJWWDVK</t>
+          <t>B0C4YSV3XL</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7407,25 +7403,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>AC-3XL</t>
+          <t>AM-W15</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Wireless Mic with Charging Case</t>
         </is>
       </c>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
-        <v>130.404042</v>
+        <v>11761.9332</v>
       </c>
       <c r="I108" t="n">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -7437,16 +7433,16 @@
         <v>29</v>
       </c>
       <c r="M108" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="O108" t="n">
         <v>1</v>
       </c>
       <c r="P108" t="n">
-        <v>17099.41</v>
+        <v>16505.6</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -7457,12 +7453,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>FBA78204</t>
+          <t>FBA79834</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>B0C4YT43Z3</t>
+          <t>B0FJ8T4WXM</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7472,25 +7468,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>AM-C31</t>
+          <t>PB-05 (AA-05 + AM-C11 + AI-04)</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Tripod</t>
+          <t>PB-05</t>
         </is>
       </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
-        <v>3835.413</v>
+        <v>5118.2854</v>
       </c>
       <c r="I109" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -7505,12 +7501,14 @@
         <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O109" t="n">
-        <v>0</v>
-      </c>
-      <c r="P109" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="P109" t="n">
+        <v>73409.8</v>
+      </c>
       <c r="Q109" t="inlineStr">
         <is>
           <t>2026-07-18</t>
@@ -7520,12 +7518,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>FBA75679</t>
+          <t>FBA79909</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>B0B4JRQP22</t>
+          <t>B0FVM17Q4W</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7535,25 +7533,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>AA-02</t>
+          <t>AM-W20</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
-        <v>1330.281037275</v>
+        <v>2164.7070972</v>
       </c>
       <c r="I110" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -7565,17 +7563,15 @@
         <v>29</v>
       </c>
       <c r="M110" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="N110" t="n">
         <v>0</v>
       </c>
       <c r="O110" t="n">
-        <v>6</v>
-      </c>
-      <c r="P110" t="n">
-        <v>259341.18</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P110" t="inlineStr"/>
       <c r="Q110" t="inlineStr">
         <is>
           <t>2026-07-18</t>
@@ -7585,12 +7581,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>FBA79967</t>
+          <t>FBA75687</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>B0G2C2RCXN</t>
+          <t>B0B4G5ZLTB</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7600,7 +7596,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>AM-W19</t>
+          <t>AM-W11</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -7610,15 +7606,15 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>Wireless Microphone</t>
         </is>
       </c>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
-        <v>1159.29193338</v>
+        <v>2857.758705882353</v>
       </c>
       <c r="I111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
@@ -7630,15 +7626,17 @@
         <v>29</v>
       </c>
       <c r="M111" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="N111" t="n">
         <v>0</v>
       </c>
       <c r="O111" t="n">
-        <v>0</v>
-      </c>
-      <c r="P111" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P111" t="n">
+        <v>1885.92</v>
+      </c>
       <c r="Q111" t="inlineStr">
         <is>
           <t>2026-07-18</t>
@@ -7648,12 +7646,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>FBA75683</t>
+          <t>FBA79816</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>B0B4G94VP3</t>
+          <t>B0FPR962YS</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7663,25 +7661,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>AA-03</t>
+          <t>AM-W22</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
-        <v>179.9635942941177</v>
+        <v>1679.60406096</v>
       </c>
       <c r="I112" t="n">
-        <v>52</v>
+        <v>173</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -7693,16 +7691,16 @@
         <v>29</v>
       </c>
       <c r="M112" t="n">
+        <v>0</v>
+      </c>
+      <c r="N112" t="n">
+        <v>164</v>
+      </c>
+      <c r="O112" t="n">
         <v>1</v>
       </c>
-      <c r="N112" t="n">
-        <v>0</v>
-      </c>
-      <c r="O112" t="n">
-        <v>0</v>
-      </c>
       <c r="P112" t="n">
-        <v>17526.55</v>
+        <v>435345.64</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -7713,12 +7711,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>FBA80085</t>
+          <t>FBA79820</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>B0GXPBHDRF</t>
+          <t>B0FQJWWDVK</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7728,25 +7726,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>M6</t>
+          <t>AC-3XL</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Audio Mixer</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>06 channels Mixer</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
-        <v>3998.590893</v>
+        <v>130.404042</v>
       </c>
       <c r="I113" t="n">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -7758,16 +7756,16 @@
         <v>29</v>
       </c>
       <c r="M113" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O113" t="n">
         <v>1</v>
       </c>
       <c r="P113" t="n">
-        <v>351516.12</v>
+        <v>17099.41</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -7778,12 +7776,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>FBA79655</t>
+          <t>FBA76864</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>B0DN6PFWNK</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7793,25 +7791,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>AM-C44 Pro</t>
+          <t>AI-04 Red</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
-        <v>3277.450944</v>
+        <v>2165.574481998618</v>
       </c>
       <c r="I114" t="n">
-        <v>26</v>
+        <v>870</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -7826,13 +7824,13 @@
         <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O114" t="n">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="P114" t="n">
-        <v>100388.06</v>
+        <v>3077071.27</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -7843,12 +7841,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>FBA75674</t>
+          <t>FBA75683</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>B0B4G19R58</t>
+          <t>B0B4G94VP3</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7858,25 +7856,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>AM-C2</t>
+          <t>AA-03</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>XLR Microphone Kit - Boomarm</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
-        <v>2119.874127397059</v>
+        <v>179.9635942941177</v>
       </c>
       <c r="I115" t="n">
-        <v>92</v>
+        <v>52</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -7891,13 +7889,13 @@
         <v>1</v>
       </c>
       <c r="N115" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="P115" t="n">
-        <v>267173.45</v>
+        <v>17526.55</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -7908,12 +7906,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>FBA76723</t>
+          <t>FBA75688</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>B0BLKF46QG</t>
+          <t>B0B4G763WS</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7923,25 +7921,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>AM-C20</t>
+          <t>AM-W12</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Microphone Wireless Handheld</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Tripod</t>
+          <t>Wireless Microphone</t>
         </is>
       </c>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
-        <v>1235.473403164659</v>
+        <v>1956.963080117647</v>
       </c>
       <c r="I116" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -7953,16 +7951,16 @@
         <v>29</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N116" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O116" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P116" t="n">
-        <v>3729.48</v>
+        <v>32295.69</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -7973,12 +7971,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>FBA79445</t>
+          <t>FBA79449</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>B0DFMLS8JG</t>
+          <t>B0DFMNGFTD</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7988,7 +7986,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>AM-W32</t>
+          <t>AM-W36</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -8003,10 +8001,10 @@
       </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
-        <v>2167.31517804</v>
+        <v>4042.525302</v>
       </c>
       <c r="I117" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -8021,13 +8019,13 @@
         <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P117" t="n">
-        <v>71574.49000000001</v>
+        <v>80319.42999999999</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -8038,12 +8036,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>FBA79961</t>
+          <t>FBA78973</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>B0G53H49BS</t>
+          <t>B0CF5R3V95</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -8053,25 +8051,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>AI-13</t>
+          <t>AA-19</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Audio Mixer</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>4 channels Mixer</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
-        <v>1544.91011775</v>
+        <v>1960.237563966397</v>
       </c>
       <c r="I118" t="n">
-        <v>454</v>
+        <v>121</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -8083,16 +8081,16 @@
         <v>29</v>
       </c>
       <c r="M118" t="n">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O118" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="P118" t="n">
-        <v>962394.0600000001</v>
+        <v>317484.46</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -8103,12 +8101,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>FBA79904</t>
+          <t>FBA79008</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>B0FTVQQVDC</t>
+          <t>B0CH4RT4P8</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -8118,25 +8116,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>PB-10 (AM-C2+AI-04+AH-60-BL)</t>
+          <t>AI-06</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>PB-10</t>
+          <t>Audio Interface</t>
         </is>
       </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
-        <v>4986.467599999999</v>
+        <v>2934.090945</v>
       </c>
       <c r="I119" t="n">
-        <v>66</v>
+        <v>14</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -8151,13 +8149,13 @@
         <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O119" t="n">
         <v>1</v>
       </c>
       <c r="P119" t="n">
-        <v>521422.71</v>
+        <v>35964.5</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -8168,12 +8166,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>FBA76730</t>
+          <t>FBA79958</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>B0BLKB6FRR</t>
+          <t>B0G3Q59X8C</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -8183,25 +8181,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>AM-C27</t>
+          <t>AM-W24</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vocal Microphone</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
-        <v>827.5708984229998</v>
+        <v>905.00405148</v>
       </c>
       <c r="I120" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -8216,13 +8214,13 @@
         <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
       </c>
       <c r="P120" t="n">
-        <v>3021.51</v>
+        <v>64650.55</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -8233,12 +8231,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>FBA79447</t>
+          <t>FBA75684</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>B0DFMLXD9S</t>
+          <t>B0B4G7VWXD</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -8248,25 +8246,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>AM-W34</t>
+          <t>AA-04</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Microphone Wireless Handheld</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Wireless Microphone</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
-        <v>2360.3131602</v>
+        <v>871.9473036705882</v>
       </c>
       <c r="I121" t="n">
-        <v>11</v>
+        <v>66</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
@@ -8278,16 +8276,16 @@
         <v>29</v>
       </c>
       <c r="M121" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N121" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O121" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="P121" t="n">
-        <v>31526.62</v>
+        <v>74884.23</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -8298,12 +8296,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>FBA76727</t>
+          <t>FBA79957</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>B0BLKCDRNB</t>
+          <t>B0G3Q517Y2</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -8313,25 +8311,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>AM-C24</t>
+          <t>AM-W23</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Tripod</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
-        <v>1676.644024574118</v>
+        <v>1566.15254442</v>
       </c>
       <c r="I122" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
@@ -8343,16 +8341,16 @@
         <v>29</v>
       </c>
       <c r="M122" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" t="n">
+        <v>51</v>
+      </c>
+      <c r="O122" t="n">
         <v>1</v>
       </c>
-      <c r="N122" t="n">
-        <v>0</v>
-      </c>
-      <c r="O122" t="n">
-        <v>2</v>
-      </c>
       <c r="P122" t="n">
-        <v>0</v>
+        <v>120235.88</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
@@ -8363,12 +8361,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>FBA79813</t>
+          <t>FBA80005</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>B0FG88HVQ8</t>
+          <t>B0GW96CQMG</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -8378,25 +8376,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>AH-50</t>
+          <t>T-835</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>DJ Headphone</t>
+          <t>Microphone Wireless Handheld</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>DJ Headphone</t>
+          <t>Quad UHF Wireless Microphone With Receiver Box</t>
         </is>
       </c>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
-        <v>1201.7320128</v>
+        <v>6259.394015999999</v>
       </c>
       <c r="I123" t="n">
-        <v>542</v>
+        <v>18</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -8411,13 +8409,13 @@
         <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="P123" t="n">
-        <v>803052.7</v>
+        <v>142206.19</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -8428,12 +8426,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>FBA79356</t>
+          <t>FBA79380</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>B0D3Q2T5XX</t>
+          <t>B0D3M1B4Z8</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8443,25 +8441,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>AA-19WL</t>
+          <t>AM-C46</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Condenser Mic with Boom Arm</t>
         </is>
       </c>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
-        <v>2973.2121576</v>
+        <v>2021.262651</v>
       </c>
       <c r="I124" t="n">
-        <v>10</v>
+        <v>298</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
@@ -8473,16 +8471,16 @@
         <v>29</v>
       </c>
       <c r="M124" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="O124" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="P124" t="n">
-        <v>32233.45</v>
+        <v>792266.62</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -8493,12 +8491,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>FBA75680</t>
+          <t>FBA78976</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>B0B4G1PXWV</t>
+          <t>B0CF5SHL15</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8508,25 +8506,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>AM-C6</t>
+          <t>AA-22</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Monitor Speakers Accessories</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Tripod</t>
+          <t>Monitor Speaker Stand Pair</t>
         </is>
       </c>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
-        <v>1815.59502123</v>
+        <v>1722.835557825</v>
       </c>
       <c r="I125" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -8538,16 +8536,16 @@
         <v>29</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N125" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P125" t="n">
-        <v>12598.26</v>
+        <v>66026.89999999999</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -8558,12 +8556,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>FBA79980</t>
+          <t>FBA79979</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>B0GN8MMKY1</t>
+          <t>B0GN8RQJRG</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8573,7 +8571,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>AK-37-W</t>
+          <t>AK-37-B</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -8583,15 +8581,15 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>37 Key Electronic Keyboard White</t>
+          <t>37 Key Electronic Keyboard Black</t>
         </is>
       </c>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
-        <v>2335.8554064</v>
+        <v>2261.3068296</v>
       </c>
       <c r="I126" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
@@ -8606,13 +8604,13 @@
         <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>3</v>
       </c>
       <c r="P126" t="n">
-        <v>13980.65</v>
+        <v>61514.88</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -8623,12 +8621,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>FBA79449</t>
+          <t>FBA75690</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>B0DFMNGFTD</t>
+          <t>B0B4K87PR4</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8638,25 +8636,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>AM-W36</t>
+          <t>AM-C10</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Microphone Wireless Handheld</t>
+          <t>Microphone Conference</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Wireless Microphone</t>
+          <t>Conference Microphone</t>
         </is>
       </c>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
-        <v>4042.525302</v>
+        <v>2311.522194589411</v>
       </c>
       <c r="I127" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
@@ -8668,16 +8666,16 @@
         <v>29</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N127" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P127" t="n">
-        <v>80319.42999999999</v>
+        <v>81298.17999999999</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -8688,12 +8686,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>FBA79107</t>
+          <t>FBA79064</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>B0CM9P5CCK</t>
+          <t>B0CJR76Y7G</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8703,25 +8701,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>AM-W17</t>
+          <t>AA-25</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Microphone Wireless Lapel</t>
+          <t>Microphone Accessories</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Wireless Lapel Microphone</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
-        <v>1043.232336</v>
+        <v>326.010105</v>
       </c>
       <c r="I128" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
@@ -8733,16 +8731,16 @@
         <v>29</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N128" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="O128" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P128" t="n">
-        <v>52327.7</v>
+        <v>18819.55</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -8753,12 +8751,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>FBA79963</t>
+          <t>FBA79842</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>B0G53CB72D</t>
+          <t>B0G4DNF8RZ</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8768,25 +8766,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>AM-Pro8</t>
+          <t>AM-C48</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Audio Mixer</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>8 channels Mixer</t>
+          <t>Microphone Dynamic</t>
         </is>
       </c>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
-        <v>12112.09532316</v>
+        <v>1956.06063</v>
       </c>
       <c r="I129" t="n">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
@@ -8801,13 +8799,13 @@
         <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P129" t="n">
-        <v>47194.42</v>
+        <v>142250.59</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -8818,12 +8816,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>FBA76862</t>
+          <t>FBA75674</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>B0BPLWW72Y</t>
+          <t>B0B4G19R58</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8833,25 +8831,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>AM-C28</t>
+          <t>AM-C2</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Microphone Conference</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Conference Microphone</t>
+          <t>XLR Microphone Kit - Boomarm</t>
         </is>
       </c>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
-        <v>874.2436631991176</v>
+        <v>2119.874127397059</v>
       </c>
       <c r="I130" t="n">
-        <v>177</v>
+        <v>92</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
@@ -8863,16 +8861,16 @@
         <v>29</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N130" t="n">
         <v>6</v>
       </c>
       <c r="O130" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="P130" t="n">
-        <v>210581.01</v>
+        <v>267173.45</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -8883,12 +8881,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>FBA80009</t>
+          <t>FBA76721</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>B0GW8R2RYM</t>
+          <t>B0BLKB55BM</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8898,25 +8896,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>AM-C51</t>
+          <t>AM-C18</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Microphone Dynamic</t>
+          <t>Microphone dynamic</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vocal Microphone</t>
+          <t>Mobile Microphone</t>
         </is>
       </c>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
-        <v>912.8282939999998</v>
+        <v>2664.193308210882</v>
       </c>
       <c r="I131" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
@@ -8937,7 +8935,7 @@
         <v>0</v>
       </c>
       <c r="P131" t="n">
-        <v>18687.28</v>
+        <v>1683.78</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -8948,12 +8946,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>FBA76414</t>
+          <t>FBA79980</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>B0BLJVJ2GN</t>
+          <t>B0GN8MMKY1</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8963,25 +8961,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>AA-05</t>
+          <t>AK-37-W</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>Electric Keyboard</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>37 Key Electronic Keyboard White</t>
         </is>
       </c>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
-        <v>280.0829144294117</v>
+        <v>2335.8554064</v>
       </c>
       <c r="I132" t="n">
-        <v>589</v>
+        <v>5</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
@@ -8993,16 +8991,16 @@
         <v>29</v>
       </c>
       <c r="M132" t="n">
+        <v>0</v>
+      </c>
+      <c r="N132" t="n">
         <v>1</v>
       </c>
-      <c r="N132" t="n">
-        <v>26</v>
-      </c>
       <c r="O132" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="P132" t="n">
-        <v>274807.88</v>
+        <v>13980.65</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -9013,12 +9011,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>FBA76725</t>
+          <t>FBA76727</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>B0BLKCSJ7Z</t>
+          <t>B0BLKCDRNB</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -9028,7 +9026,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>AM-C22</t>
+          <t>AM-C24</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -9043,10 +9041,10 @@
       </c>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="n">
-        <v>849.3751611646587</v>
+        <v>1676.644024574118</v>
       </c>
       <c r="I133" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -9058,13 +9056,13 @@
         <v>29</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N133" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P133" t="n">
         <v>0</v>
@@ -9078,12 +9076,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>FBA79105</t>
+          <t>FBA79005</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>B0CM6WH4ZT</t>
+          <t>B0CKHVHVQ1</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -9093,25 +9091,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>AI-12</t>
+          <t>AM-W45</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>Microphone Conference</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>Wireless Conference Microphone</t>
         </is>
       </c>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
-        <v>678.1010183999999</v>
+        <v>2738.484882</v>
       </c>
       <c r="I134" t="n">
-        <v>100</v>
+        <v>574</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
@@ -9123,16 +9121,16 @@
         <v>29</v>
       </c>
       <c r="M134" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>66</v>
+        <v>2</v>
       </c>
       <c r="O134" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="P134" t="n">
-        <v>94324.98</v>
+        <v>2197559.03</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -9143,12 +9141,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>FBA76722</t>
+          <t>FBA79904</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>B0BLKDC4PP</t>
+          <t>B0FTVQQVDC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -9158,25 +9156,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>AM-C19</t>
+          <t>PB-10 (AM-C2+AI-04+AH-60-BL)</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Tripod</t>
+          <t>PB-10</t>
         </is>
       </c>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="n">
-        <v>1642.572937873306</v>
+        <v>4986.467599999999</v>
       </c>
       <c r="I135" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
@@ -9194,9 +9192,11 @@
         <v>0</v>
       </c>
       <c r="O135" t="n">
-        <v>0</v>
-      </c>
-      <c r="P135" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P135" t="n">
+        <v>521422.71</v>
+      </c>
       <c r="Q135" t="inlineStr">
         <is>
           <t>2026-07-18</t>
@@ -9206,12 +9206,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>FBA79840</t>
+          <t>FBA79722</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>B0FQBWV1ST</t>
+          <t>B0F2HYY7JF</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -9221,25 +9221,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>AH-60-RD</t>
+          <t>AM-W21</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Headphone</t>
+          <t>Microphone Wireless Lapel</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Headphone</t>
+          <t>Wireless Lapel Microphone</t>
         </is>
       </c>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
-        <v>1092.483648</v>
+        <v>2803.686903</v>
       </c>
       <c r="I136" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
@@ -9257,10 +9257,10 @@
         <v>0</v>
       </c>
       <c r="O136" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P136" t="n">
-        <v>52666.76</v>
+        <v>14763.09</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
@@ -9271,12 +9271,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>FBA79448</t>
+          <t>FBA76725</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>B0DFMKY4TT</t>
+          <t>B0BLKCSJ7Z</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -9286,25 +9286,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>AM-W35</t>
+          <t>AM-C22</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Microphone Wireless Handheld</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Wireless Microphone</t>
+          <t>USB Microphone Kit - Tripod</t>
         </is>
       </c>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
-        <v>1984.74951924</v>
+        <v>849.3751611646587</v>
       </c>
       <c r="I137" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
@@ -9319,13 +9319,13 @@
         <v>0</v>
       </c>
       <c r="N137" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P137" t="n">
-        <v>57775.88</v>
+        <v>0</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -9336,12 +9336,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>FBA76721</t>
+          <t>FBA79824</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>B0BLKB55BM</t>
+          <t>B0FJ2K95XT</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -9351,25 +9351,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>AM-C18</t>
+          <t>GB-01 (AM-C43 +AI-10)</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Microphone dynamic</t>
+          <t>Bundles</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mobile Microphone</t>
+          <t>GB-01</t>
         </is>
       </c>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="n">
-        <v>2664.193308210882</v>
+        <v>2585.9936</v>
       </c>
       <c r="I138" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
@@ -9384,13 +9384,13 @@
         <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P138" t="n">
-        <v>1683.78</v>
+        <v>46140.06</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
@@ -9401,12 +9401,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>FBA75673</t>
+          <t>FBA75689</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>B0B4DPX2J2</t>
+          <t>B0B4G59Y8W</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -9416,25 +9416,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>AM-C1</t>
+          <t>AM-W13</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Microphone Condenser</t>
+          <t>Microphone Wireless Handheld</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>USB Microphone Kit - Boomarm</t>
+          <t>Wireless Microphone</t>
         </is>
       </c>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
-        <v>1475.964687829412</v>
+        <v>1305.459898830882</v>
       </c>
       <c r="I139" t="n">
-        <v>2480</v>
+        <v>20</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
@@ -9446,16 +9446,16 @@
         <v>29</v>
       </c>
       <c r="M139" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N139" t="n">
-        <v>205</v>
+        <v>1</v>
       </c>
       <c r="O139" t="n">
-        <v>197</v>
+        <v>4</v>
       </c>
       <c r="P139" t="n">
-        <v>4726055.07</v>
+        <v>32691.99</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
@@ -9466,12 +9466,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>FBA79008</t>
+          <t>FBA79813</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>B0CH4RT4P8</t>
+          <t>B0FG88HVQ8</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -9481,25 +9481,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>AI-06</t>
+          <t>AH-50</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>DJ Headphone</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Audio Interface</t>
+          <t>DJ Headphone</t>
         </is>
       </c>
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
-        <v>2934.090945</v>
+        <v>1201.7320128</v>
       </c>
       <c r="I140" t="n">
-        <v>14</v>
+        <v>542</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
@@ -9514,13 +9514,13 @@
         <v>0</v>
       </c>
       <c r="N140" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="O140" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="P140" t="n">
-        <v>35964.5</v>
+        <v>803052.7</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
@@ -9531,12 +9531,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>FBA79832</t>
+          <t>FBA79009</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>B0FJ8S53GW</t>
+          <t>B0CH4PMR8K</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9546,25 +9546,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>GB-05 (AM-C43 + AI-06)</t>
+          <t>AM-C41</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Bundles</t>
+          <t>Microphone Condenser</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>GB-05</t>
+          <t>USB Microphone Kit - Tripod</t>
         </is>
       </c>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="n">
-        <v>3909.104</v>
+        <v>1043.232336</v>
       </c>
       <c r="I141" t="n">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
@@ -9579,13 +9579,13 @@
         <v>0</v>
       </c>
       <c r="N141" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="O141" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P141" t="n">
-        <v>83681.85000000001</v>
+        <v>53597.14</v>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
@@ -9596,12 +9596,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>FBA75684</t>
+          <t>FBA79839</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>B0B4G7VWXD</t>
+          <t>B0FQBXS6Y2</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -9611,25 +9611,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>AA-04</t>
+          <t>AH-45 BK</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Microphone Accessories</t>
+          <t>DJ Headphone</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>DJ Headphone</t>
         </is>
       </c>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="n">
-        <v>871.9473036705882</v>
+        <v>614.5220519999999</v>
       </c>
       <c r="I142" t="n">
-        <v>66</v>
+        <v>217</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
@@ -9641,16 +9641,16 @@
         <v>29</v>
       </c>
       <c r="M142" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="N142" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O142" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P142" t="n">
-        <v>74884.23</v>
+        <v>240999.64</v>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
